--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_ADJR2.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,68 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -358,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -390,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -425,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -601,2379 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="14" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-4.9685235080517122E-2</v>
+        <v>-0.05290805228241287</v>
       </c>
       <c r="C2">
-        <v>-9.3995073104699914E-2</v>
+        <v>-0.09443372468019956</v>
       </c>
       <c r="D2">
-        <v>-9.1108951820758385E-2</v>
+        <v>-0.09126380938006122</v>
       </c>
       <c r="E2">
-        <v>-7.8718176775406476E-2</v>
+        <v>-0.07399877926477889</v>
       </c>
       <c r="F2">
-        <v>-9.7232032609756033E-2</v>
+        <v>-0.09241042489189458</v>
       </c>
       <c r="G2">
-        <v>-0.1025521831156771</v>
+        <v>-0.09754132334002055</v>
       </c>
       <c r="H2">
-        <v>-3.5288128444634789E-2</v>
+        <v>-0.03574552227493144</v>
       </c>
       <c r="I2">
-        <v>1.9141869028561919E-2</v>
+        <v>0.02164721650338612</v>
       </c>
       <c r="J2">
-        <v>-2.265062922617149E-2</v>
+        <v>-0.01506384052866705</v>
       </c>
       <c r="K2">
-        <v>2.7277147680145081E-2</v>
+        <v>0.02926372003213413</v>
       </c>
       <c r="L2">
-        <v>0.11958000733813701</v>
+        <v>0.1126649665114981</v>
       </c>
       <c r="M2">
-        <v>0.14448555136842581</v>
+        <v>0.1431542778907414</v>
       </c>
       <c r="N2">
-        <v>0.25103595399697609</v>
+        <v>0.2506907001058473</v>
       </c>
       <c r="O2">
-        <v>0.33898672935219498</v>
+        <v>0.337638069859681</v>
       </c>
       <c r="P2">
-        <v>0.37720054065633812</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3788698974968241</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-2.1496991682709781E-2</v>
+        <v>-0.02338977500364613</v>
       </c>
       <c r="C3">
-        <v>-0.19553524369805439</v>
+        <v>-0.2005140104515763</v>
       </c>
       <c r="D3">
-        <v>-0.13439763853215339</v>
+        <v>-0.1336381738029375</v>
       </c>
       <c r="E3">
-        <v>1.064913253867442E-2</v>
+        <v>0.01189838638913474</v>
       </c>
       <c r="F3">
-        <v>8.8537518129814224E-2</v>
+        <v>0.096576438331663</v>
       </c>
       <c r="G3">
-        <v>0.15270819643194691</v>
+        <v>0.15034460181354</v>
       </c>
       <c r="H3">
-        <v>0.2138869338218822</v>
+        <v>0.2068370342305458</v>
       </c>
       <c r="I3">
-        <v>0.24101757296216281</v>
+        <v>0.2308688696167037</v>
       </c>
       <c r="J3">
-        <v>0.29084581128781339</v>
+        <v>0.2770922267672325</v>
       </c>
       <c r="K3">
-        <v>0.32599206796935298</v>
+        <v>0.3085641985620685</v>
       </c>
       <c r="L3">
-        <v>0.3145257064901042</v>
+        <v>0.3038172183834741</v>
       </c>
       <c r="M3">
-        <v>0.31401006271918319</v>
+        <v>0.3001693282739456</v>
       </c>
       <c r="N3">
-        <v>0.28416644105696259</v>
+        <v>0.2718381996675007</v>
       </c>
       <c r="O3">
-        <v>0.26258514565358998</v>
+        <v>0.2618310565870506</v>
       </c>
       <c r="P3">
-        <v>0.28014841285636699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.2795035035171569</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-4.3628622121103362E-2</v>
+        <v>-0.0428466917420348</v>
       </c>
       <c r="C4">
-        <v>-6.7992770698319174E-2</v>
+        <v>-0.06111144707903773</v>
       </c>
       <c r="D4">
-        <v>-0.14464726156769031</v>
+        <v>-0.1360344163531771</v>
       </c>
       <c r="E4">
-        <v>-0.15234657889560499</v>
+        <v>-0.1330592574692104</v>
       </c>
       <c r="F4">
-        <v>-0.20949640351753529</v>
+        <v>-0.190699294789714</v>
       </c>
       <c r="G4">
-        <v>-9.0886603255216622E-2</v>
+        <v>-0.08282408736231285</v>
       </c>
       <c r="H4">
-        <v>-4.2229003320247106E-3</v>
+        <v>0.01328630784015376</v>
       </c>
       <c r="I4">
-        <v>4.2367162514714077E-2</v>
+        <v>0.05917543654447926</v>
       </c>
       <c r="J4">
-        <v>4.9159031277617067E-2</v>
+        <v>0.06003981550784616</v>
       </c>
       <c r="K4">
-        <v>0.13221266246002319</v>
+        <v>0.128891342948196</v>
       </c>
       <c r="L4">
-        <v>0.20180420445747671</v>
+        <v>0.203927389445575</v>
       </c>
       <c r="M4">
-        <v>0.26882604202165478</v>
+        <v>0.2686259895627416</v>
       </c>
       <c r="N4">
-        <v>0.29968424890304368</v>
+        <v>0.3006960808422861</v>
       </c>
       <c r="O4">
-        <v>0.3025696858600701</v>
+        <v>0.3044819192176804</v>
       </c>
       <c r="P4">
-        <v>0.2838031555161758</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.2883521766904619</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-3.2648194467335211E-2</v>
+        <v>-0.03312243053805321</v>
       </c>
       <c r="C5">
-        <v>-9.5565187794171752E-2</v>
+        <v>-0.1079856605714667</v>
       </c>
       <c r="D5">
-        <v>-5.7767285381953179E-2</v>
+        <v>-0.05459503733835095</v>
       </c>
       <c r="E5">
-        <v>-0.15602085314316</v>
+        <v>-0.1533703686752587</v>
       </c>
       <c r="F5">
-        <v>4.7812965373866832E-2</v>
+        <v>0.04500865097458337</v>
       </c>
       <c r="G5">
-        <v>0.1465374736174152</v>
+        <v>0.140069127099583</v>
       </c>
       <c r="H5">
-        <v>0.17478190495539431</v>
+        <v>0.1693533787621279</v>
       </c>
       <c r="I5">
-        <v>0.243786306345432</v>
+        <v>0.2433539035224792</v>
       </c>
       <c r="J5">
-        <v>0.32281333914007909</v>
+        <v>0.3180588361562025</v>
       </c>
       <c r="K5">
-        <v>0.3520222745137932</v>
+        <v>0.3489745368898846</v>
       </c>
       <c r="L5">
-        <v>0.38670271908465248</v>
+        <v>0.3763020465304756</v>
       </c>
       <c r="M5">
-        <v>0.38962130231524572</v>
+        <v>0.3728807720822168</v>
       </c>
       <c r="N5">
-        <v>0.36791791884215502</v>
+        <v>0.3450381085123028</v>
       </c>
       <c r="O5">
-        <v>0.34875919326653509</v>
+        <v>0.3228496262300381</v>
       </c>
       <c r="P5">
-        <v>0.31952703330371202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.2982882160189976</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-3.392028554912082E-2</v>
+        <v>-0.04125468019205144</v>
       </c>
       <c r="C6">
-        <v>-0.1224516319158072</v>
+        <v>-0.1260005161593283</v>
       </c>
       <c r="D6">
-        <v>-7.2342983769902419E-2</v>
+        <v>-0.07472468280652299</v>
       </c>
       <c r="E6">
-        <v>-0.10729167607572811</v>
+        <v>-0.1059164955041367</v>
       </c>
       <c r="F6">
-        <v>0.11336926204315941</v>
+        <v>0.1220747841336962</v>
       </c>
       <c r="G6">
-        <v>0.20479974728140221</v>
+        <v>0.2161262494102473</v>
       </c>
       <c r="H6">
-        <v>0.25590535130775399</v>
+        <v>0.2746259590753149</v>
       </c>
       <c r="I6">
-        <v>0.33362770954523868</v>
+        <v>0.3459763203635747</v>
       </c>
       <c r="J6">
-        <v>0.37807976965642781</v>
+        <v>0.3881054825802105</v>
       </c>
       <c r="K6">
-        <v>0.39202568402784299</v>
+        <v>0.4035709836089363</v>
       </c>
       <c r="L6">
-        <v>0.41125340480224509</v>
+        <v>0.4237128868756384</v>
       </c>
       <c r="M6">
-        <v>0.41941973043136122</v>
+        <v>0.423067537669095</v>
       </c>
       <c r="N6">
-        <v>0.40951717778866381</v>
+        <v>0.4141939030950985</v>
       </c>
       <c r="O6">
-        <v>0.41383397712959219</v>
+        <v>0.4177925070200633</v>
       </c>
       <c r="P6">
-        <v>0.39125412297377499</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3980682099023359</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-4.4421799230516618E-2</v>
+        <v>-0.04909751690350871</v>
       </c>
       <c r="C7">
-        <v>-6.4779510689083108E-2</v>
+        <v>-0.0736802005837856</v>
       </c>
       <c r="D7">
-        <v>-0.13295035909097611</v>
+        <v>-0.1418812321450353</v>
       </c>
       <c r="E7">
-        <v>-0.1563117964373073</v>
+        <v>-0.166917769578189</v>
       </c>
       <c r="F7">
-        <v>-0.22426392784342461</v>
+        <v>-0.2299105953192488</v>
       </c>
       <c r="G7">
-        <v>-0.17506981745473749</v>
+        <v>-0.1833269736810698</v>
       </c>
       <c r="H7">
-        <v>-5.1808404396216097E-2</v>
+        <v>-0.06090437602934785</v>
       </c>
       <c r="I7">
-        <v>2.9353677323270259E-2</v>
+        <v>0.03096514335234943</v>
       </c>
       <c r="J7">
-        <v>6.1436673384968797E-2</v>
+        <v>0.05937293358241083</v>
       </c>
       <c r="K7">
-        <v>8.2994021816216457E-2</v>
+        <v>0.07702919702022842</v>
       </c>
       <c r="L7">
-        <v>0.18045246401766829</v>
+        <v>0.1663863395715357</v>
       </c>
       <c r="M7">
-        <v>0.25432307092147882</v>
+        <v>0.2416368530020362</v>
       </c>
       <c r="N7">
-        <v>0.30202836556385643</v>
+        <v>0.2913360647965418</v>
       </c>
       <c r="O7">
-        <v>0.32250492766713651</v>
+        <v>0.3198451662837481</v>
       </c>
       <c r="P7">
-        <v>0.32860396245925488</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.324847176752883</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-4.1595462191052653E-2</v>
+        <v>-0.04161676453248285</v>
       </c>
       <c r="C8">
-        <v>-7.3314979312563838E-2</v>
+        <v>-0.07057973858627373</v>
       </c>
       <c r="D8">
-        <v>-0.1505874905095887</v>
+        <v>-0.1416418503408551</v>
       </c>
       <c r="E8">
-        <v>-0.18897846677306709</v>
+        <v>-0.1841140903868618</v>
       </c>
       <c r="F8">
-        <v>-0.1281001324079421</v>
+        <v>-0.116649992358776</v>
       </c>
       <c r="G8">
-        <v>-8.7148563225570106E-3</v>
+        <v>-0.01159558520438136</v>
       </c>
       <c r="H8">
-        <v>7.96511722815379E-3</v>
+        <v>0.002520041407645481</v>
       </c>
       <c r="I8">
-        <v>0.1068398718125316</v>
+        <v>0.1065358913817622</v>
       </c>
       <c r="J8">
-        <v>0.15407877859611549</v>
+        <v>0.144366519885698</v>
       </c>
       <c r="K8">
-        <v>0.26817023820025743</v>
+        <v>0.2649601125690919</v>
       </c>
       <c r="L8">
-        <v>0.27671848134202631</v>
+        <v>0.28527948609592</v>
       </c>
       <c r="M8">
-        <v>0.32878623032641818</v>
+        <v>0.3309250211665592</v>
       </c>
       <c r="N8">
-        <v>0.35622465877809528</v>
+        <v>0.3553589923148681</v>
       </c>
       <c r="O8">
-        <v>0.35475535715281042</v>
+        <v>0.3554175993741481</v>
       </c>
       <c r="P8">
-        <v>0.34179546482013762</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.3380462752054365</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-3.8672054981212192E-2</v>
+        <v>-0.03607211251945661</v>
       </c>
       <c r="C9">
-        <v>-6.6532765264413068E-2</v>
+        <v>-0.06618608712226516</v>
       </c>
       <c r="D9">
-        <v>-0.13247604734065449</v>
+        <v>-0.1340323915188795</v>
       </c>
       <c r="E9">
-        <v>-0.15886293236167801</v>
+        <v>-0.1582107314652125</v>
       </c>
       <c r="F9">
-        <v>-0.1063084964682072</v>
+        <v>-0.1084794204748158</v>
       </c>
       <c r="G9">
-        <v>-2.304438646886074E-3</v>
+        <v>-0.002529489497045507</v>
       </c>
       <c r="H9">
-        <v>5.73255530950589E-3</v>
+        <v>0.01234063892225965</v>
       </c>
       <c r="I9">
-        <v>0.105860110073335</v>
+        <v>0.1110449185537352</v>
       </c>
       <c r="J9">
-        <v>0.13980383241236741</v>
+        <v>0.1419693006268327</v>
       </c>
       <c r="K9">
-        <v>0.28861825136046437</v>
+        <v>0.2950826625093015</v>
       </c>
       <c r="L9">
-        <v>0.2847487932754651</v>
+        <v>0.2914990300899697</v>
       </c>
       <c r="M9">
-        <v>0.33129573996992678</v>
+        <v>0.3361571278411461</v>
       </c>
       <c r="N9">
-        <v>0.35868840336897978</v>
+        <v>0.3652434933016384</v>
       </c>
       <c r="O9">
-        <v>0.35779904404376839</v>
+        <v>0.3584917404340702</v>
       </c>
       <c r="P9">
-        <v>0.35630093144919672</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3574368941203669</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-4.3015916699960667E-2</v>
+        <v>-0.04436179603757926</v>
       </c>
       <c r="C10">
-        <v>-7.3575320054658333E-2</v>
+        <v>-0.06975792298954123</v>
       </c>
       <c r="D10">
-        <v>-0.1391119885237809</v>
+        <v>-0.1358701835681858</v>
       </c>
       <c r="E10">
-        <v>-0.1742037364811958</v>
+        <v>-0.1686031173526272</v>
       </c>
       <c r="F10">
-        <v>-0.1237784340228399</v>
+        <v>-0.1147508276794303</v>
       </c>
       <c r="G10">
-        <v>-1.173953861749274E-2</v>
+        <v>-0.01438681787367518</v>
       </c>
       <c r="H10">
-        <v>-9.0022550046513997E-4</v>
+        <v>0.00764717993509962</v>
       </c>
       <c r="I10">
-        <v>0.10624414909379711</v>
+        <v>0.1005976557766696</v>
       </c>
       <c r="J10">
-        <v>0.1292450573140739</v>
+        <v>0.1275128425245546</v>
       </c>
       <c r="K10">
-        <v>0.28193632310257799</v>
+        <v>0.2922363191494189</v>
       </c>
       <c r="L10">
-        <v>0.27036972650684082</v>
+        <v>0.2738511236655066</v>
       </c>
       <c r="M10">
-        <v>0.31153638295210639</v>
+        <v>0.319100694959749</v>
       </c>
       <c r="N10">
-        <v>0.33603832931667432</v>
+        <v>0.3520255984220858</v>
       </c>
       <c r="O10">
-        <v>0.33368823972436468</v>
+        <v>0.3425410242127483</v>
       </c>
       <c r="P10">
-        <v>0.33452259375946353</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3450864745727105</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-3.9968684129271341E-2</v>
+        <v>-0.03969628540689531</v>
       </c>
       <c r="C11">
-        <v>-6.8108792129805862E-2</v>
+        <v>-0.07027569620302601</v>
       </c>
       <c r="D11">
-        <v>-0.13767083737910149</v>
+        <v>-0.1420095071475114</v>
       </c>
       <c r="E11">
-        <v>-0.15962528847983809</v>
+        <v>-0.1789542672539678</v>
       </c>
       <c r="F11">
-        <v>-0.11863307178916151</v>
+        <v>-0.1265133851181932</v>
       </c>
       <c r="G11">
-        <v>-1.1797533167314319E-2</v>
+        <v>-0.01177472964020464</v>
       </c>
       <c r="H11">
-        <v>-5.744199870330537E-3</v>
+        <v>-0.006069604479411798</v>
       </c>
       <c r="I11">
-        <v>9.8635376721562237E-2</v>
+        <v>0.1025672093117999</v>
       </c>
       <c r="J11">
-        <v>0.12857805062517841</v>
+        <v>0.1346634198528251</v>
       </c>
       <c r="K11">
-        <v>0.28829624051053798</v>
+        <v>0.2911464398552266</v>
       </c>
       <c r="L11">
-        <v>0.29317657418974702</v>
+        <v>0.2935264437604828</v>
       </c>
       <c r="M11">
-        <v>0.33868749095494149</v>
+        <v>0.3355304121454212</v>
       </c>
       <c r="N11">
-        <v>0.36477538977196272</v>
+        <v>0.3584664162819911</v>
       </c>
       <c r="O11">
-        <v>0.35820812150595888</v>
+        <v>0.3547477660320685</v>
       </c>
       <c r="P11">
-        <v>0.35842609333293951</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3515386512891109</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-3.9296776939202409E-2</v>
+        <v>-0.0346307935781022</v>
       </c>
       <c r="C12">
-        <v>-0.1049535117370524</v>
+        <v>-0.1078839043058303</v>
       </c>
       <c r="D12">
-        <v>-5.980074262934152E-2</v>
+        <v>-0.05417091129565035</v>
       </c>
       <c r="E12">
-        <v>-0.14532154344103679</v>
+        <v>-0.1577660157634832</v>
       </c>
       <c r="F12">
-        <v>4.1629951308627608E-2</v>
+        <v>0.02697042290836292</v>
       </c>
       <c r="G12">
-        <v>9.8620629371537802E-2</v>
+        <v>0.09240585211540434</v>
       </c>
       <c r="H12">
-        <v>0.20858393434583181</v>
+        <v>0.2017873445031116</v>
       </c>
       <c r="I12">
-        <v>0.31345941049368348</v>
+        <v>0.3139854298249561</v>
       </c>
       <c r="J12">
-        <v>0.37375803978012612</v>
+        <v>0.3752649026421077</v>
       </c>
       <c r="K12">
-        <v>0.40394513963206091</v>
+        <v>0.4056492773492206</v>
       </c>
       <c r="L12">
-        <v>0.4344603962800262</v>
+        <v>0.4381332842070348</v>
       </c>
       <c r="M12">
-        <v>0.43886293885595368</v>
+        <v>0.4418204208437043</v>
       </c>
       <c r="N12">
-        <v>0.41807742203745291</v>
+        <v>0.4232338586271512</v>
       </c>
       <c r="O12">
-        <v>0.39751807582610421</v>
+        <v>0.4008036707787858</v>
       </c>
       <c r="P12">
-        <v>0.35844988100897712</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.3663172775784367</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-4.4655057381580772E-2</v>
+        <v>-0.04913895576458743</v>
       </c>
       <c r="C13">
-        <v>-0.186818091881778</v>
+        <v>-0.1894446586768078</v>
       </c>
       <c r="D13">
-        <v>-0.11836969786330929</v>
+        <v>-0.1083141069980394</v>
       </c>
       <c r="E13">
-        <v>-0.16692166060309879</v>
+        <v>-0.1631794853789215</v>
       </c>
       <c r="F13">
-        <v>-0.1644161552848683</v>
+        <v>-0.1526732075581595</v>
       </c>
       <c r="G13">
-        <v>-2.4196438713357679E-2</v>
+        <v>-0.008121960627004311</v>
       </c>
       <c r="H13">
-        <v>-1.348097452622634E-2</v>
+        <v>-0.004027723758630037</v>
       </c>
       <c r="I13">
-        <v>3.5424557054821129E-2</v>
+        <v>0.04656211036215092</v>
       </c>
       <c r="J13">
-        <v>0.12216489685824231</v>
+        <v>0.1196291661391424</v>
       </c>
       <c r="K13">
-        <v>0.1996179185755293</v>
+        <v>0.1998711389252364</v>
       </c>
       <c r="L13">
-        <v>0.21125592764987161</v>
+        <v>0.2088850523414892</v>
       </c>
       <c r="M13">
-        <v>0.24091251048298959</v>
+        <v>0.2319156624246561</v>
       </c>
       <c r="N13">
-        <v>0.24374816809592981</v>
+        <v>0.2378089985964852</v>
       </c>
       <c r="O13">
-        <v>0.26409705099696429</v>
+        <v>0.2551540197076286</v>
       </c>
       <c r="P13">
-        <v>0.25260282850320548</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.2482487881448251</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-4.7260478410381258E-2</v>
+        <v>-0.04808359499714973</v>
       </c>
       <c r="C14">
-        <v>-6.9080870970323435E-2</v>
+        <v>-0.06989451551362991</v>
       </c>
       <c r="D14">
-        <v>-0.13387839415739139</v>
+        <v>-0.1359592397017341</v>
       </c>
       <c r="E14">
-        <v>-0.14997455711509811</v>
+        <v>-0.1530254182300488</v>
       </c>
       <c r="F14">
-        <v>-0.2070142500828121</v>
+        <v>-0.2184645555625079</v>
       </c>
       <c r="G14">
-        <v>-0.1643682005919111</v>
+        <v>-0.1691453372634291</v>
       </c>
       <c r="H14">
-        <v>-5.1483531175584213E-2</v>
+        <v>-0.06452942683433724</v>
       </c>
       <c r="I14">
-        <v>3.1439369067922357E-2</v>
+        <v>0.02753580605314065</v>
       </c>
       <c r="J14">
-        <v>5.8723212801700543E-2</v>
+        <v>0.04629384918900526</v>
       </c>
       <c r="K14">
-        <v>8.2614726763017524E-2</v>
+        <v>0.07711068128584031</v>
       </c>
       <c r="L14">
-        <v>0.18634923619979959</v>
+        <v>0.1819680445369364</v>
       </c>
       <c r="M14">
-        <v>0.29965935389389858</v>
+        <v>0.2957630443815166</v>
       </c>
       <c r="N14">
-        <v>0.33603122980861511</v>
+        <v>0.3294373927558529</v>
       </c>
       <c r="O14">
-        <v>0.36860835258901481</v>
+        <v>0.3582996416016216</v>
       </c>
       <c r="P14">
-        <v>0.3889362015253382</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3841058031065494</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-4.9309270624202747E-2</v>
+        <v>-0.05173732756432053</v>
       </c>
       <c r="C15">
-        <v>-7.0643470091513463E-2</v>
+        <v>-0.07387379987922131</v>
       </c>
       <c r="D15">
-        <v>-0.13850308750901549</v>
+        <v>-0.1391800687413293</v>
       </c>
       <c r="E15">
-        <v>-0.1545595924161256</v>
+        <v>-0.1551677339159433</v>
       </c>
       <c r="F15">
-        <v>-0.21836079110459439</v>
+        <v>-0.2207788171001065</v>
       </c>
       <c r="G15">
-        <v>-0.17066763464796469</v>
+        <v>-0.1768674468017013</v>
       </c>
       <c r="H15">
-        <v>-6.5697182381940153E-2</v>
+        <v>-0.06427439069833023</v>
       </c>
       <c r="I15">
-        <v>1.179871135532483E-2</v>
+        <v>0.008967489720978421</v>
       </c>
       <c r="J15">
-        <v>4.4285584209138543E-2</v>
+        <v>0.03554955756247546</v>
       </c>
       <c r="K15">
-        <v>6.069610807328709E-2</v>
+        <v>0.06604659091536209</v>
       </c>
       <c r="L15">
-        <v>0.15227660340105409</v>
+        <v>0.1610332049896538</v>
       </c>
       <c r="M15">
-        <v>0.26441030807137472</v>
+        <v>0.263589153249133</v>
       </c>
       <c r="N15">
-        <v>0.30644651694510172</v>
+        <v>0.3041205993509052</v>
       </c>
       <c r="O15">
-        <v>0.33435213938056829</v>
+        <v>0.3269921843701488</v>
       </c>
       <c r="P15">
-        <v>0.35179175221539749</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3508115932889618</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-4.4180028178068327E-2</v>
+        <v>-0.04446687221492027</v>
       </c>
       <c r="C16">
-        <v>-6.8196090293645539E-2</v>
+        <v>-0.0667859988670014</v>
       </c>
       <c r="D16">
-        <v>-0.13801290026490051</v>
+        <v>-0.1330920695925161</v>
       </c>
       <c r="E16">
-        <v>-0.16155675310241971</v>
+        <v>-0.1482428139168927</v>
       </c>
       <c r="F16">
-        <v>-0.22503102446264089</v>
+        <v>-0.2061264177841818</v>
       </c>
       <c r="G16">
-        <v>-0.1847836306461228</v>
+        <v>-0.173022460913709</v>
       </c>
       <c r="H16">
-        <v>-7.3911866773483006E-2</v>
+        <v>-0.0734038769405486</v>
       </c>
       <c r="I16">
-        <v>3.860412892335022E-3</v>
+        <v>0.0166553908256214</v>
       </c>
       <c r="J16">
-        <v>3.1433431370947909E-2</v>
+        <v>0.0475133385834571</v>
       </c>
       <c r="K16">
-        <v>4.9001959963483173E-2</v>
+        <v>0.06818775118554758</v>
       </c>
       <c r="L16">
-        <v>0.1453340164903654</v>
+        <v>0.1548809851226433</v>
       </c>
       <c r="M16">
-        <v>0.2570141856596716</v>
+        <v>0.2613204978487123</v>
       </c>
       <c r="N16">
-        <v>0.29795866045498898</v>
+        <v>0.3093014510542064</v>
       </c>
       <c r="O16">
-        <v>0.33175410680130091</v>
+        <v>0.3427064481324344</v>
       </c>
       <c r="P16">
-        <v>0.362686909615199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.3609336804059972</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-4.504745344091441E-2</v>
+        <v>-0.04572540764015509</v>
       </c>
       <c r="C17">
-        <v>-6.9722566402567146E-2</v>
+        <v>-0.07038254004729763</v>
       </c>
       <c r="D17">
-        <v>-0.13567220888224901</v>
+        <v>-0.1386711192880916</v>
       </c>
       <c r="E17">
-        <v>-0.1587077193010801</v>
+        <v>-0.1568524062136907</v>
       </c>
       <c r="F17">
-        <v>-0.217400768957144</v>
+        <v>-0.2068771992387269</v>
       </c>
       <c r="G17">
-        <v>-0.17459370172325081</v>
+        <v>-0.1757930834748186</v>
       </c>
       <c r="H17">
-        <v>-7.1430158593434309E-2</v>
+        <v>-0.06828710596107102</v>
       </c>
       <c r="I17">
-        <v>9.4222813146100631E-3</v>
+        <v>0.02163875727083861</v>
       </c>
       <c r="J17">
-        <v>2.8009355503935171E-2</v>
+        <v>0.03663451699611057</v>
       </c>
       <c r="K17">
-        <v>4.2853457059292013E-2</v>
+        <v>0.05192965616571638</v>
       </c>
       <c r="L17">
-        <v>0.12601415553352591</v>
+        <v>0.1318304182993626</v>
       </c>
       <c r="M17">
-        <v>0.22775040402722771</v>
+        <v>0.2347247332788074</v>
       </c>
       <c r="N17">
-        <v>0.27410475231012388</v>
+        <v>0.2687167490995108</v>
       </c>
       <c r="O17">
-        <v>0.31103099943344542</v>
+        <v>0.3007002963299794</v>
       </c>
       <c r="P17">
-        <v>0.33241716825831891</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.3195156908433222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-3.6279148859252992E-2</v>
+        <v>-0.03324441172796243</v>
       </c>
       <c r="C18">
-        <v>-0.10437027296330149</v>
+        <v>-0.111873061215821</v>
       </c>
       <c r="D18">
-        <v>-6.518138614770741E-2</v>
+        <v>-0.05671004413398262</v>
       </c>
       <c r="E18">
-        <v>-0.16054153016039799</v>
+        <v>-0.1638915953642512</v>
       </c>
       <c r="F18">
-        <v>5.0108040625405553E-2</v>
+        <v>0.06233836615829323</v>
       </c>
       <c r="G18">
-        <v>0.12893623707558841</v>
+        <v>0.1398011461922045</v>
       </c>
       <c r="H18">
-        <v>0.20995111048963999</v>
+        <v>0.216513369919801</v>
       </c>
       <c r="I18">
-        <v>0.30235447240247409</v>
+        <v>0.3064404133723341</v>
       </c>
       <c r="J18">
-        <v>0.36880955117911568</v>
+        <v>0.3702879597033081</v>
       </c>
       <c r="K18">
-        <v>0.39332297984938058</v>
+        <v>0.3896170179771432</v>
       </c>
       <c r="L18">
-        <v>0.41364594200421773</v>
+        <v>0.4150460230905175</v>
       </c>
       <c r="M18">
-        <v>0.41792141309023789</v>
+        <v>0.4233206098792784</v>
       </c>
       <c r="N18">
-        <v>0.3943355915638142</v>
+        <v>0.3950193390999827</v>
       </c>
       <c r="O18">
-        <v>0.37381074349288151</v>
+        <v>0.3724735410620446</v>
       </c>
       <c r="P18">
-        <v>0.35420526558947169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.3512037421869109</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-3.9295120278190848E-2</v>
+        <v>-0.03747800578326009</v>
       </c>
       <c r="C19">
-        <v>-0.1338623002889783</v>
+        <v>-0.1391249362925348</v>
       </c>
       <c r="D19">
-        <v>-9.5257639886315165E-2</v>
+        <v>-0.09751963475036277</v>
       </c>
       <c r="E19">
-        <v>-0.13363641430372211</v>
+        <v>-0.1485559962969979</v>
       </c>
       <c r="F19">
-        <v>0.12179831445320211</v>
+        <v>0.1110496794115069</v>
       </c>
       <c r="G19">
-        <v>0.20432215693660591</v>
+        <v>0.1955476426615595</v>
       </c>
       <c r="H19">
-        <v>0.27243368662779061</v>
+        <v>0.2696519303855587</v>
       </c>
       <c r="I19">
-        <v>0.35409804421814067</v>
+        <v>0.3502012457951504</v>
       </c>
       <c r="J19">
-        <v>0.4057120505981977</v>
+        <v>0.3964427780747922</v>
       </c>
       <c r="K19">
-        <v>0.41739849209921659</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.43547316472074932</v>
+        <v>0.4092652347595571</v>
+      </c>
+      <c r="L19">
+        <v>0.4322564284528748</v>
       </c>
       <c r="M19">
-        <v>0.4344520760215585</v>
+        <v>0.4346961299285406</v>
       </c>
       <c r="N19">
-        <v>0.42067329836681772</v>
+        <v>0.427781846224992</v>
       </c>
       <c r="O19">
-        <v>0.42731994585475108</v>
+        <v>0.4293157470341714</v>
       </c>
       <c r="P19">
-        <v>0.41831273275746361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4167370986831487</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-3.9736733503420447E-2</v>
+        <v>-0.03691273779090799</v>
       </c>
       <c r="C20">
-        <v>-0.15819114903840259</v>
+        <v>-0.1470038550428454</v>
       </c>
       <c r="D20">
-        <v>-0.1074145062485726</v>
+        <v>-0.1084806214982055</v>
       </c>
       <c r="E20">
-        <v>-1.389713584393077E-2</v>
+        <v>-0.01817334624716842</v>
       </c>
       <c r="F20">
-        <v>0.1040397183785905</v>
+        <v>0.0913296051771481</v>
       </c>
       <c r="G20">
-        <v>0.1404909144398658</v>
+        <v>0.1161355191973047</v>
       </c>
       <c r="H20">
-        <v>0.22783302823013479</v>
+        <v>0.213492732844479</v>
       </c>
       <c r="I20">
-        <v>0.30828812501052899</v>
+        <v>0.2985283521661847</v>
       </c>
       <c r="J20">
-        <v>0.34737149504696851</v>
+        <v>0.340126685116913</v>
       </c>
       <c r="K20">
-        <v>0.39635751124165469</v>
+        <v>0.3844635314955261</v>
       </c>
       <c r="L20">
-        <v>0.40223465571773531</v>
+        <v>0.3931755789314698</v>
       </c>
       <c r="M20">
-        <v>0.40828020008059979</v>
+        <v>0.397289770629951</v>
       </c>
       <c r="N20">
-        <v>0.44875226909140981</v>
+        <v>0.436570651877731</v>
       </c>
       <c r="O20">
-        <v>0.44889688061130101</v>
+        <v>0.4371537737006477</v>
       </c>
       <c r="P20">
-        <v>0.45232865942280259</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.4331722122125706</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-2.5281933442113821E-2</v>
+        <v>-0.02334707594584575</v>
       </c>
       <c r="C21">
-        <v>-0.17989064716356151</v>
+        <v>-0.1866885854365806</v>
       </c>
       <c r="D21">
-        <v>-0.1208881091653643</v>
+        <v>-0.1348516536432175</v>
       </c>
       <c r="E21">
-        <v>1.1936473502157119E-2</v>
+        <v>-0.01362758374560174</v>
       </c>
       <c r="F21">
-        <v>6.6082905042107676E-2</v>
+        <v>0.05189538556187611</v>
       </c>
       <c r="G21">
-        <v>9.092473934340585E-2</v>
+        <v>0.08137399859106384</v>
       </c>
       <c r="H21">
-        <v>0.13748603591343811</v>
+        <v>0.1363534809165161</v>
       </c>
       <c r="I21">
-        <v>0.19625611065855991</v>
+        <v>0.1771938216111085</v>
       </c>
       <c r="J21">
-        <v>0.2552448900541639</v>
+        <v>0.2567529391222928</v>
       </c>
       <c r="K21">
-        <v>0.29773135853382549</v>
+        <v>0.2923893779586586</v>
       </c>
       <c r="L21">
-        <v>0.31244796459824598</v>
+        <v>0.3083295716797269</v>
       </c>
       <c r="M21">
-        <v>0.29444747517256359</v>
+        <v>0.2923539091645606</v>
       </c>
       <c r="N21">
-        <v>0.25472463996833428</v>
+        <v>0.2604942805217177</v>
       </c>
       <c r="O21">
-        <v>0.2309108300876927</v>
+        <v>0.2391474668012657</v>
       </c>
       <c r="P21">
-        <v>0.23862616430691949</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.2489051300180811</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.9993350396702959E-2</v>
+        <v>-0.02325415210536807</v>
       </c>
       <c r="C22">
-        <v>-0.17802035979371841</v>
+        <v>-0.1831882922030569</v>
       </c>
       <c r="D22">
-        <v>-0.1160839278150175</v>
+        <v>-0.127459371179816</v>
       </c>
       <c r="E22">
-        <v>7.819029703144631E-3</v>
+        <v>0.007992810066180699</v>
       </c>
       <c r="F22">
-        <v>6.6418179291750576E-2</v>
+        <v>0.06220966402277668</v>
       </c>
       <c r="G22">
-        <v>8.5343360405348581E-2</v>
+        <v>0.08162106584404358</v>
       </c>
       <c r="H22">
-        <v>0.11379403543805371</v>
+        <v>0.1098006311829648</v>
       </c>
       <c r="I22">
-        <v>0.13931731223417701</v>
+        <v>0.1286881853650335</v>
       </c>
       <c r="J22">
-        <v>0.20780852273689771</v>
+        <v>0.1970431490551278</v>
       </c>
       <c r="K22">
-        <v>0.2544999005950937</v>
+        <v>0.2387557792789213</v>
       </c>
       <c r="L22">
-        <v>0.2630621326747265</v>
+        <v>0.2487954062366606</v>
       </c>
       <c r="M22">
-        <v>0.26872510867507682</v>
+        <v>0.2537606883678764</v>
       </c>
       <c r="N22">
-        <v>0.25209054207387288</v>
+        <v>0.2351152877833492</v>
       </c>
       <c r="O22">
-        <v>0.2468617237699165</v>
+        <v>0.2294834846096991</v>
       </c>
       <c r="P22">
-        <v>0.24555724174206189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.2278860071787831</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-3.7672906617533503E-2</v>
+        <v>-0.0332648932388941</v>
       </c>
       <c r="C23">
-        <v>-0.15070275789157181</v>
+        <v>-0.1474635156474073</v>
       </c>
       <c r="D23">
-        <v>-4.3319296616564362E-2</v>
+        <v>-0.02314808568866864</v>
       </c>
       <c r="E23">
-        <v>7.4190605262950168E-2</v>
+        <v>0.07485751941415106</v>
       </c>
       <c r="F23">
-        <v>0.21221165867025649</v>
+        <v>0.2188420234410367</v>
       </c>
       <c r="G23">
-        <v>0.302001900829239</v>
+        <v>0.3077272637854154</v>
       </c>
       <c r="H23">
-        <v>0.33569530056918712</v>
+        <v>0.33997949760891</v>
       </c>
       <c r="I23">
-        <v>0.35209973223644109</v>
+        <v>0.3571745328183167</v>
       </c>
       <c r="J23">
-        <v>0.37519391664180279</v>
+        <v>0.3749224052706704</v>
       </c>
       <c r="K23">
-        <v>0.37331336254577591</v>
+        <v>0.3690144964077461</v>
       </c>
       <c r="L23">
-        <v>0.36976911580233279</v>
+        <v>0.3623151035989186</v>
       </c>
       <c r="M23">
-        <v>0.35125474088296887</v>
+        <v>0.3464388218896167</v>
       </c>
       <c r="N23">
-        <v>0.34670892090184058</v>
+        <v>0.3404914154570609</v>
       </c>
       <c r="O23">
-        <v>0.34345042764668848</v>
+        <v>0.3365238836832427</v>
       </c>
       <c r="P23">
-        <v>0.32298965780249322</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.3188225708429546</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-3.683169783862187E-2</v>
+        <v>-0.03704864118662871</v>
       </c>
       <c r="C24">
-        <v>-1.9777387639885189E-3</v>
+        <v>-0.002002338917554225</v>
       </c>
       <c r="D24">
-        <v>6.732819374304512E-2</v>
+        <v>0.05932466672562654</v>
       </c>
       <c r="E24">
-        <v>-5.1587329493683011E-3</v>
+        <v>-0.01286902784468392</v>
       </c>
       <c r="F24">
-        <v>-2.3713032378160449E-2</v>
+        <v>-0.03004712281138456</v>
       </c>
       <c r="G24">
-        <v>-7.3343858300569789E-2</v>
+        <v>-0.08407976969448272</v>
       </c>
       <c r="H24">
-        <v>-6.3924529872929514E-2</v>
+        <v>-0.07419585036678898</v>
       </c>
       <c r="I24">
-        <v>-8.8277605463247699E-2</v>
+        <v>-0.1008812543978504</v>
       </c>
       <c r="J24">
-        <v>-0.16727614446915051</v>
+        <v>-0.178393088025166</v>
       </c>
       <c r="K24">
-        <v>-0.31355368442728537</v>
+        <v>-0.32477519089324</v>
       </c>
       <c r="L24">
-        <v>-0.29541066390419218</v>
+        <v>-0.3172201425195673</v>
       </c>
       <c r="M24">
-        <v>-0.32934379419392268</v>
+        <v>-0.3514604612904818</v>
       </c>
       <c r="N24">
-        <v>-0.41640371045168229</v>
+        <v>-0.4465053461935005</v>
       </c>
       <c r="O24">
-        <v>-0.48913216883804578</v>
+        <v>-0.5200335447926416</v>
       </c>
       <c r="P24">
-        <v>-0.61346829069195374</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>-0.6291734173444823</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-0.1629647792929709</v>
+        <v>-0.1538840890504212</v>
       </c>
       <c r="C25">
-        <v>-0.1077293789094514</v>
+        <v>-0.09835657641436842</v>
       </c>
       <c r="D25">
-        <v>-0.1161549487621354</v>
+        <v>-0.108564905364894</v>
       </c>
       <c r="E25">
-        <v>-8.9402830379826756E-2</v>
+        <v>-0.08699783951237504</v>
       </c>
       <c r="F25">
-        <v>-0.15335170689076361</v>
+        <v>-0.1400483703015639</v>
       </c>
       <c r="G25">
-        <v>-0.22620033524438979</v>
+        <v>-0.2098346658443764</v>
       </c>
       <c r="H25">
-        <v>-0.21913162798155289</v>
+        <v>-0.2100571360642922</v>
       </c>
       <c r="I25">
-        <v>-0.17402669327494549</v>
+        <v>-0.1694189313138174</v>
       </c>
       <c r="J25">
-        <v>-0.20948006681514611</v>
+        <v>-0.2110169390920211</v>
       </c>
       <c r="K25">
-        <v>-0.2975094359186029</v>
+        <v>-0.3059412987308207</v>
       </c>
       <c r="L25">
-        <v>-0.34772900038312238</v>
+        <v>-0.3597690442681867</v>
       </c>
       <c r="M25">
-        <v>-0.44096112655404029</v>
+        <v>-0.4557987830411553</v>
       </c>
       <c r="N25">
-        <v>-0.54817113110672822</v>
+        <v>-0.5670208490379528</v>
       </c>
       <c r="O25">
-        <v>-0.60357765291898613</v>
+        <v>-0.6198940909768103</v>
       </c>
       <c r="P25">
-        <v>-0.65339296273891034</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>-0.6587941394194394</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-6.6017806270928861E-2</v>
+        <v>-0.06769430620935239</v>
       </c>
       <c r="C26">
-        <v>-3.4070467057786109E-2</v>
+        <v>-0.03155757069003653</v>
       </c>
       <c r="D26">
-        <v>4.9044222530320279E-2</v>
+        <v>0.04522458476251955</v>
       </c>
       <c r="E26">
-        <v>6.9800388612603542E-2</v>
+        <v>0.06624728714623511</v>
       </c>
       <c r="F26">
-        <v>8.185879761140645E-2</v>
+        <v>0.07952192304942816</v>
       </c>
       <c r="G26">
-        <v>0.1231731821023799</v>
+        <v>0.114604609246579</v>
       </c>
       <c r="H26">
-        <v>0.13705105949086649</v>
+        <v>0.1279840957462619</v>
       </c>
       <c r="I26">
-        <v>0.1292187273527278</v>
+        <v>0.1319066326383234</v>
       </c>
       <c r="J26">
-        <v>0.16967507171787061</v>
+        <v>0.1682671328457477</v>
       </c>
       <c r="K26">
-        <v>0.19313555224400811</v>
+        <v>0.200951297503126</v>
       </c>
       <c r="L26">
-        <v>0.16561720158826121</v>
+        <v>0.1704369540537202</v>
       </c>
       <c r="M26">
-        <v>0.18226815573272129</v>
+        <v>0.1894170947358042</v>
       </c>
       <c r="N26">
-        <v>0.1682009931987076</v>
+        <v>0.1624707189988562</v>
       </c>
       <c r="O26">
-        <v>0.13632345839176149</v>
+        <v>0.1391649537943931</v>
       </c>
       <c r="P26">
-        <v>0.14034096286490161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.139093383117885</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-0.12274863111861881</v>
+        <v>-0.1177491306962133</v>
       </c>
       <c r="C27">
-        <v>-8.2472375577978915E-2</v>
+        <v>-0.07936111006377725</v>
       </c>
       <c r="D27">
-        <v>0.1125334396992393</v>
+        <v>0.1127821438566733</v>
       </c>
       <c r="E27">
-        <v>0.13743157907917841</v>
+        <v>0.123417757396492</v>
       </c>
       <c r="F27">
-        <v>0.1116236873669693</v>
+        <v>0.1095093909276492</v>
       </c>
       <c r="G27">
-        <v>0.1048887550463138</v>
+        <v>0.1031714104304308</v>
       </c>
       <c r="H27">
-        <v>9.5994083550633741E-2</v>
+        <v>0.09469399050862777</v>
       </c>
       <c r="I27">
-        <v>4.4328890208824162E-2</v>
+        <v>0.05453247405299842</v>
       </c>
       <c r="J27">
-        <v>9.4751049556572153E-2</v>
+        <v>0.1003498755139523</v>
       </c>
       <c r="K27">
-        <v>0.11117946692145</v>
+        <v>0.1131704319528546</v>
       </c>
       <c r="L27">
-        <v>0.1521810908055645</v>
+        <v>0.1453961880174357</v>
       </c>
       <c r="M27">
-        <v>0.18941304858551941</v>
+        <v>0.1852858585269199</v>
       </c>
       <c r="N27">
-        <v>0.18363533964053019</v>
+        <v>0.1845330164842665</v>
       </c>
       <c r="O27">
-        <v>0.1540913778726242</v>
+        <v>0.1556550667037292</v>
       </c>
       <c r="P27">
-        <v>0.12902673827620881</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.1379463004350393</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-6.4193757787664119E-2</v>
+        <v>-0.0632991169876408</v>
       </c>
       <c r="C28">
-        <v>-0.11427932435438511</v>
+        <v>-0.1172730905491431</v>
       </c>
       <c r="D28">
-        <v>-0.17477974193198159</v>
+        <v>-0.1726349806042995</v>
       </c>
       <c r="E28">
-        <v>-0.1315526780729516</v>
+        <v>-0.1323277613228749</v>
       </c>
       <c r="F28">
-        <v>-0.1100737019409839</v>
+        <v>-0.1144762218058361</v>
       </c>
       <c r="G28">
-        <v>-5.9957153167284657E-2</v>
+        <v>-0.05941504249098303</v>
       </c>
       <c r="H28">
-        <v>-0.11335801217616601</v>
+        <v>-0.1111156245582144</v>
       </c>
       <c r="I28">
-        <v>-5.6274827195457858E-2</v>
+        <v>-0.05073479102647802</v>
       </c>
       <c r="J28">
-        <v>8.7385399424209573E-2</v>
+        <v>0.07661386684639453</v>
       </c>
       <c r="K28">
-        <v>0.19173610885980591</v>
+        <v>0.1949439467972967</v>
       </c>
       <c r="L28">
-        <v>0.22562136721363649</v>
+        <v>0.2283541557249356</v>
       </c>
       <c r="M28">
-        <v>0.20623083936054021</v>
+        <v>0.2024768790704256</v>
       </c>
       <c r="N28">
-        <v>0.14671834677436371</v>
+        <v>0.1449732336300044</v>
       </c>
       <c r="O28">
-        <v>8.4798421367701549E-2</v>
+        <v>0.08638835057250711</v>
       </c>
       <c r="P28">
-        <v>9.6283516506471822E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.003409890382121704</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-7.0566027251500033E-2</v>
+        <v>-0.07196788188040393</v>
       </c>
       <c r="C29">
-        <v>-0.12832190636390689</v>
+        <v>-0.1263451147757605</v>
       </c>
       <c r="D29">
-        <v>-0.187467523979954</v>
+        <v>-0.1853313620109307</v>
       </c>
       <c r="E29">
-        <v>-0.14096851958624959</v>
+        <v>-0.1390069977771699</v>
       </c>
       <c r="F29">
-        <v>-0.1118703448065393</v>
+        <v>-0.1158826113618496</v>
       </c>
       <c r="G29">
-        <v>-9.3054427762764153E-2</v>
+        <v>-0.09576157281215601</v>
       </c>
       <c r="H29">
-        <v>-0.19476649291112089</v>
+        <v>-0.1871818630358162</v>
       </c>
       <c r="I29">
-        <v>-0.1412717104646625</v>
+        <v>-0.1177998441673872</v>
       </c>
       <c r="J29">
-        <v>-4.7154752033673572E-2</v>
+        <v>-0.0398165057973846</v>
       </c>
       <c r="K29">
-        <v>0.1678733636862362</v>
+        <v>0.1630119236427803</v>
       </c>
       <c r="L29">
-        <v>0.19157156780905429</v>
+        <v>0.1946879863177396</v>
       </c>
       <c r="M29">
-        <v>0.21014529587373951</v>
+        <v>0.2148545580193726</v>
       </c>
       <c r="N29">
-        <v>0.18395283369554949</v>
+        <v>0.1884002797957177</v>
       </c>
       <c r="O29">
-        <v>0.13117483681597231</v>
+        <v>0.1367678550590738</v>
       </c>
       <c r="P29">
-        <v>6.1812471777467293E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.07205838668401079</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-7.0960003442138472E-2</v>
+        <v>-0.06820513997892179</v>
       </c>
       <c r="C30">
-        <v>-0.13470250532306791</v>
+        <v>-0.1284330252703835</v>
       </c>
       <c r="D30">
-        <v>-0.15320408624080531</v>
+        <v>-0.1413239421058465</v>
       </c>
       <c r="E30">
-        <v>-9.0098246232145088E-2</v>
+        <v>-0.08127428697157135</v>
       </c>
       <c r="F30">
-        <v>-0.1247819526361155</v>
+        <v>-0.1285553506051063</v>
       </c>
       <c r="G30">
-        <v>-9.3529994961356749E-2</v>
+        <v>-0.0917413188328708</v>
       </c>
       <c r="H30">
-        <v>2.0146538871210339E-2</v>
+        <v>0.008786651344780058</v>
       </c>
       <c r="I30">
-        <v>-4.715023366351604E-2</v>
+        <v>-0.05189460781608372</v>
       </c>
       <c r="J30">
-        <v>9.5807683533263216E-2</v>
+        <v>0.08542049197444335</v>
       </c>
       <c r="K30">
-        <v>0.17696149317198401</v>
+        <v>0.1746613578725854</v>
       </c>
       <c r="L30">
-        <v>0.18492068449423629</v>
+        <v>0.1920376319685738</v>
       </c>
       <c r="M30">
-        <v>0.15825728950657439</v>
+        <v>0.1727758125080888</v>
       </c>
       <c r="N30">
-        <v>0.1171157669017652</v>
+        <v>0.1366976301183994</v>
       </c>
       <c r="O30">
-        <v>5.6685101470479837E-2</v>
+        <v>0.07136848068773045</v>
       </c>
       <c r="P30">
-        <v>-2.7962891027846739E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>-0.01427525921144934</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-6.6943979105147364E-2</v>
+        <v>-0.06870663570746816</v>
       </c>
       <c r="C31">
-        <v>-0.12917984778318001</v>
+        <v>-0.135707065632097</v>
       </c>
       <c r="D31">
-        <v>-0.14152279544608501</v>
+        <v>-0.1502166609367696</v>
       </c>
       <c r="E31">
-        <v>-8.9071282691239359E-2</v>
+        <v>-0.09180169800958521</v>
       </c>
       <c r="F31">
-        <v>-0.1198720360685812</v>
+        <v>-0.1263864416903532</v>
       </c>
       <c r="G31">
-        <v>-9.3927284499356153E-2</v>
+        <v>-0.09989851253912072</v>
       </c>
       <c r="H31">
-        <v>1.86858710628912E-3</v>
+        <v>0.001074478903998138</v>
       </c>
       <c r="I31">
-        <v>-4.9453726930440249E-2</v>
+        <v>-0.07005202890519818</v>
       </c>
       <c r="J31">
-        <v>5.9255760211279783E-2</v>
+        <v>0.05342118177142945</v>
       </c>
       <c r="K31">
-        <v>0.1859059067638163</v>
+        <v>0.1904718640678881</v>
       </c>
       <c r="L31">
-        <v>0.2445614542222477</v>
+        <v>0.2506366605116659</v>
       </c>
       <c r="M31">
-        <v>0.27747132828314169</v>
+        <v>0.28578657963637</v>
       </c>
       <c r="N31">
-        <v>0.29231791412771502</v>
+        <v>0.3004243207230877</v>
       </c>
       <c r="O31">
-        <v>0.25486500839777693</v>
+        <v>0.2713710449747964</v>
       </c>
       <c r="P31">
-        <v>0.24913958836644071</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2672551840714802</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-6.9451356677875942E-2</v>
+        <v>-0.06859594505090776</v>
       </c>
       <c r="C32">
-        <v>-0.13000891147669361</v>
+        <v>-0.1213314881623954</v>
       </c>
       <c r="D32">
-        <v>-0.1807025227827348</v>
+        <v>-0.1771534559419859</v>
       </c>
       <c r="E32">
-        <v>-0.14084968285144259</v>
+        <v>-0.1318607279293237</v>
       </c>
       <c r="F32">
-        <v>-0.11583737111977251</v>
+        <v>-0.112314809775858</v>
       </c>
       <c r="G32">
-        <v>-9.817059157589024E-2</v>
+        <v>-0.09721119758310345</v>
       </c>
       <c r="H32">
-        <v>-0.1624105210467407</v>
+        <v>-0.1641335290817526</v>
       </c>
       <c r="I32">
-        <v>-0.1319944457044597</v>
+        <v>-0.1334759373032737</v>
       </c>
       <c r="J32">
-        <v>-6.3273965551636668E-2</v>
+        <v>-0.06980341848804272</v>
       </c>
       <c r="K32">
-        <v>0.14028205156821949</v>
+        <v>0.1347600666480337</v>
       </c>
       <c r="L32">
-        <v>0.19161176384689499</v>
+        <v>0.1934858914475961</v>
       </c>
       <c r="M32">
-        <v>0.22010570528011489</v>
+        <v>0.2227309699209402</v>
       </c>
       <c r="N32">
-        <v>0.2294056178076237</v>
+        <v>0.2438827665366646</v>
       </c>
       <c r="O32">
-        <v>0.23483365240051571</v>
+        <v>0.242348523228873</v>
       </c>
       <c r="P32">
-        <v>0.2270812567517031</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.2439521585617669</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-7.16248199077123E-2</v>
+        <v>-0.07036897738487655</v>
       </c>
       <c r="C33">
-        <v>-0.13001798231796599</v>
+        <v>-0.1263309138545373</v>
       </c>
       <c r="D33">
-        <v>-0.18548563659317799</v>
+        <v>-0.1805692241981733</v>
       </c>
       <c r="E33">
-        <v>-0.13989067353051499</v>
+        <v>-0.1355897630033474</v>
       </c>
       <c r="F33">
-        <v>-0.115082370092239</v>
+        <v>-0.1140028018707257</v>
       </c>
       <c r="G33">
-        <v>-9.5637678183928557E-2</v>
+        <v>-0.08853019301788766</v>
       </c>
       <c r="H33">
-        <v>-0.16845687580384941</v>
+        <v>-0.1524610618094583</v>
       </c>
       <c r="I33">
-        <v>-0.12926732731360949</v>
+        <v>-0.1174742260544559</v>
       </c>
       <c r="J33">
-        <v>-6.5483075439716057E-2</v>
+        <v>-0.05695712387994414</v>
       </c>
       <c r="K33">
-        <v>0.14551319516889619</v>
+        <v>0.1569104610474031</v>
       </c>
       <c r="L33">
-        <v>0.20202919746818401</v>
+        <v>0.2081470236714941</v>
       </c>
       <c r="M33">
-        <v>0.24210279355804909</v>
+        <v>0.2400377928718302</v>
       </c>
       <c r="N33">
-        <v>0.25740335675731008</v>
+        <v>0.2616902778732573</v>
       </c>
       <c r="O33">
-        <v>0.27026270305988842</v>
+        <v>0.2735577487026976</v>
       </c>
       <c r="P33">
-        <v>0.27062094596635272</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2797437532114339</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-6.839309227932916E-2</v>
+        <v>-0.06477972953569183</v>
       </c>
       <c r="C34">
-        <v>-0.12583608535029511</v>
+        <v>-0.1202359181252856</v>
       </c>
       <c r="D34">
-        <v>-0.179159987490218</v>
+        <v>-0.1780635537894118</v>
       </c>
       <c r="E34">
-        <v>-0.13664028421020979</v>
+        <v>-0.136086799783359</v>
       </c>
       <c r="F34">
-        <v>-0.1200173298150663</v>
+        <v>-0.1086013436232022</v>
       </c>
       <c r="G34">
-        <v>-9.6352942944846698E-2</v>
+        <v>-0.08689985619288525</v>
       </c>
       <c r="H34">
-        <v>-0.16148532328059231</v>
+        <v>-0.1542448600861833</v>
       </c>
       <c r="I34">
-        <v>-0.1312292978633848</v>
+        <v>-0.1295109162250171</v>
       </c>
       <c r="J34">
-        <v>-7.0901033245555453E-2</v>
+        <v>-0.07298023806954683</v>
       </c>
       <c r="K34">
-        <v>0.13666012792076301</v>
+        <v>0.1322908915018159</v>
       </c>
       <c r="L34">
-        <v>0.18990586484813629</v>
+        <v>0.1913387604796723</v>
       </c>
       <c r="M34">
-        <v>0.2337881023972509</v>
+        <v>0.2277903447694553</v>
       </c>
       <c r="N34">
-        <v>0.24560837999685439</v>
+        <v>0.2442521896184235</v>
       </c>
       <c r="O34">
-        <v>0.26024894271739762</v>
+        <v>0.2603460709151706</v>
       </c>
       <c r="P34">
-        <v>0.26201172359648001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2672428206104647</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-7.5707687102070806E-2</v>
+        <v>-0.06790359372289742</v>
       </c>
       <c r="C35">
-        <v>-0.13532723966104199</v>
+        <v>-0.1273036036303487</v>
       </c>
       <c r="D35">
-        <v>-0.1897118989801142</v>
+        <v>-0.1834179561283044</v>
       </c>
       <c r="E35">
-        <v>-0.14774646051098969</v>
+        <v>-0.1408448801758455</v>
       </c>
       <c r="F35">
-        <v>-0.12818335186774041</v>
+        <v>-0.1201896392944322</v>
       </c>
       <c r="G35">
-        <v>-0.102837138188241</v>
+        <v>-0.1013665555359216</v>
       </c>
       <c r="H35">
-        <v>-0.17052329671289221</v>
+        <v>-0.1701584875691325</v>
       </c>
       <c r="I35">
-        <v>-0.14619139280244331</v>
+        <v>-0.1526963503378759</v>
       </c>
       <c r="J35">
-        <v>-0.10132705528195959</v>
+        <v>-0.1028148443600772</v>
       </c>
       <c r="K35">
-        <v>0.1012437022921398</v>
+        <v>0.09212965610655255</v>
       </c>
       <c r="L35">
-        <v>0.16316455235969829</v>
+        <v>0.1599783713314962</v>
       </c>
       <c r="M35">
-        <v>0.20069134920471279</v>
+        <v>0.1984236331966803</v>
       </c>
       <c r="N35">
-        <v>0.23367296477994701</v>
+        <v>0.2325993538599241</v>
       </c>
       <c r="O35">
-        <v>0.25012575180953528</v>
+        <v>0.2462679976127063</v>
       </c>
       <c r="P35">
-        <v>0.2727220222368843</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2724713821490897</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-6.808759513201465E-2</v>
+        <v>-0.07213391851144066</v>
       </c>
       <c r="C36">
-        <v>-0.1251682650202342</v>
+        <v>-0.1351381094511152</v>
       </c>
       <c r="D36">
-        <v>-0.17964018380828109</v>
+        <v>-0.1861796798324898</v>
       </c>
       <c r="E36">
-        <v>-0.13840819338048871</v>
+        <v>-0.1380635306930806</v>
       </c>
       <c r="F36">
-        <v>-0.1121504735208964</v>
+        <v>-0.1213255157727176</v>
       </c>
       <c r="G36">
-        <v>-9.7075878554941708E-2</v>
+        <v>-0.1031196871506879</v>
       </c>
       <c r="H36">
-        <v>-0.16493657453317051</v>
+        <v>-0.1816512023480471</v>
       </c>
       <c r="I36">
-        <v>-0.12686782819532461</v>
+        <v>-0.1336578699415704</v>
       </c>
       <c r="J36">
-        <v>-5.7280217657977313E-2</v>
+        <v>-0.06871182882532151</v>
       </c>
       <c r="K36">
-        <v>0.1520415593416666</v>
+        <v>0.1525699599214748</v>
       </c>
       <c r="L36">
-        <v>0.2032950163448059</v>
+        <v>0.2001574959473314</v>
       </c>
       <c r="M36">
-        <v>0.22912398110859311</v>
+        <v>0.2393891922822466</v>
       </c>
       <c r="N36">
-        <v>0.2406354140828027</v>
+        <v>0.247664877492109</v>
       </c>
       <c r="O36">
-        <v>0.23304928797309071</v>
+        <v>0.2357844166244329</v>
       </c>
       <c r="P36">
-        <v>0.2131379110527156</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.2179801808868348</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-6.4328899018476451E-2</v>
+        <v>-0.06454228510022107</v>
       </c>
       <c r="C37">
-        <v>-0.1198064908807423</v>
+        <v>-0.1170581244658114</v>
       </c>
       <c r="D37">
-        <v>-0.17331116508186781</v>
+        <v>-0.1685230307634781</v>
       </c>
       <c r="E37">
-        <v>-0.1325330126761772</v>
+        <v>-0.1286991140679777</v>
       </c>
       <c r="F37">
-        <v>-0.1110373785353804</v>
+        <v>-0.1026973343568726</v>
       </c>
       <c r="G37">
-        <v>-8.7951975169673208E-2</v>
+        <v>-0.08700583672619647</v>
       </c>
       <c r="H37">
-        <v>-0.16213467301851919</v>
+        <v>-0.1526654126139095</v>
       </c>
       <c r="I37">
-        <v>-0.1277987750126692</v>
+        <v>-0.1210936745463851</v>
       </c>
       <c r="J37">
-        <v>-6.1453400836438757E-2</v>
+        <v>-0.06027440656875037</v>
       </c>
       <c r="K37">
-        <v>0.1529405806869153</v>
+        <v>0.1549736812785978</v>
       </c>
       <c r="L37">
-        <v>0.1984730131561083</v>
+        <v>0.2009921909146425</v>
       </c>
       <c r="M37">
-        <v>0.23593348536498329</v>
+        <v>0.2350732631338462</v>
       </c>
       <c r="N37">
-        <v>0.23665729605231031</v>
+        <v>0.2383605441085976</v>
       </c>
       <c r="O37">
-        <v>0.23388758731191109</v>
+        <v>0.2339551979577679</v>
       </c>
       <c r="P37">
-        <v>0.2135560043498807</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.215000919759591</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-7.123024412222248E-2</v>
+        <v>-0.06840291074110766</v>
       </c>
       <c r="C38">
-        <v>-0.13052168921221771</v>
+        <v>-0.1240253908900541</v>
       </c>
       <c r="D38">
-        <v>-0.1884782565192229</v>
+        <v>-0.1757527072770099</v>
       </c>
       <c r="E38">
-        <v>-0.13937828778013439</v>
+        <v>-0.1260678251495131</v>
       </c>
       <c r="F38">
-        <v>-0.1175245668064404</v>
+        <v>-0.1042532588916724</v>
       </c>
       <c r="G38">
-        <v>-9.5063146909712348E-2</v>
+        <v>-0.08192876986831378</v>
       </c>
       <c r="H38">
-        <v>-0.1625178111018688</v>
+        <v>-0.1414770221243416</v>
       </c>
       <c r="I38">
-        <v>-0.12147986450931771</v>
+        <v>-0.1153480303952318</v>
       </c>
       <c r="J38">
-        <v>-6.2002880591622449E-2</v>
+        <v>-0.05413327439363137</v>
       </c>
       <c r="K38">
-        <v>0.14508010430902221</v>
+        <v>0.1506842528625256</v>
       </c>
       <c r="L38">
-        <v>0.1954244657105135</v>
+        <v>0.1989662170504564</v>
       </c>
       <c r="M38">
-        <v>0.23025766252940319</v>
+        <v>0.2298094633009626</v>
       </c>
       <c r="N38">
-        <v>0.23500677475691209</v>
+        <v>0.2416132513100487</v>
       </c>
       <c r="O38">
-        <v>0.2327835563720311</v>
+        <v>0.250967047710334</v>
       </c>
       <c r="P38">
-        <v>0.22353074322806979</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.2307279913714461</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-6.8946452711157624E-2</v>
+        <v>-0.07056549107845415</v>
       </c>
       <c r="C39">
-        <v>-0.12828433486688651</v>
+        <v>-0.1285210767342237</v>
       </c>
       <c r="D39">
-        <v>-0.18670479872381579</v>
+        <v>-0.1809159051540844</v>
       </c>
       <c r="E39">
-        <v>-0.14180633503376691</v>
+        <v>-0.1384791670646799</v>
       </c>
       <c r="F39">
-        <v>-0.1222412093474539</v>
+        <v>-0.1113555858077296</v>
       </c>
       <c r="G39">
-        <v>-9.8971349528883243E-2</v>
+        <v>-0.09427409692311653</v>
       </c>
       <c r="H39">
-        <v>-0.17154079172193901</v>
+        <v>-0.1604388020159296</v>
       </c>
       <c r="I39">
-        <v>-0.1364121400651071</v>
+        <v>-0.1280778490391062</v>
       </c>
       <c r="J39">
-        <v>-8.1565702135141541E-2</v>
+        <v>-0.06580792466900268</v>
       </c>
       <c r="K39">
-        <v>0.1224651288799216</v>
+        <v>0.1405305281617102</v>
       </c>
       <c r="L39">
-        <v>0.17698384262263209</v>
+        <v>0.1864114933886935</v>
       </c>
       <c r="M39">
-        <v>0.20902333615203031</v>
+        <v>0.2232575210656438</v>
       </c>
       <c r="N39">
-        <v>0.22784817266197729</v>
+        <v>0.2334214865097475</v>
       </c>
       <c r="O39">
-        <v>0.2333222226811226</v>
+        <v>0.238274921913971</v>
       </c>
       <c r="P39">
-        <v>0.22757194244816251</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.2251361479085535</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-6.8737313517325718E-2</v>
+        <v>-0.07008391229590191</v>
       </c>
       <c r="C40">
-        <v>-0.12984313167114411</v>
+        <v>-0.1246390809867833</v>
       </c>
       <c r="D40">
-        <v>-0.18508215573426581</v>
+        <v>-0.1746652881136437</v>
       </c>
       <c r="E40">
-        <v>-0.13976281014843059</v>
+        <v>-0.1315818480630474</v>
       </c>
       <c r="F40">
-        <v>-0.1161968411688766</v>
+        <v>-0.1114689274671427</v>
       </c>
       <c r="G40">
-        <v>-9.1054973510054121E-2</v>
+        <v>-0.09157122030274076</v>
       </c>
       <c r="H40">
-        <v>-0.14538815350407119</v>
+        <v>-0.1539180825266186</v>
       </c>
       <c r="I40">
-        <v>-0.12285154607780251</v>
+        <v>-0.1265828903320223</v>
       </c>
       <c r="J40">
-        <v>-7.17029846644857E-2</v>
+        <v>-0.07101044696595016</v>
       </c>
       <c r="K40">
-        <v>0.10987684386996691</v>
+        <v>0.1193249762433043</v>
       </c>
       <c r="L40">
-        <v>0.17332256069754909</v>
+        <v>0.1806939235331631</v>
       </c>
       <c r="M40">
-        <v>0.19476468338729541</v>
+        <v>0.2126597009920072</v>
       </c>
       <c r="N40">
-        <v>0.22688156641765281</v>
+        <v>0.2443278447232455</v>
       </c>
       <c r="O40">
-        <v>0.2470543441649298</v>
+        <v>0.2574297301517016</v>
       </c>
       <c r="P40">
-        <v>0.27194453511508221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.285306998278389</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-0.1118446996679827</v>
+        <v>-0.1127519278908456</v>
       </c>
       <c r="C41">
-        <v>-0.17314468594967661</v>
+        <v>-0.1845773529806243</v>
       </c>
       <c r="D41">
-        <v>-0.1043739212810358</v>
+        <v>-0.1184118162536127</v>
       </c>
       <c r="E41">
-        <v>-2.663004739608154E-2</v>
+        <v>-0.03027874800478101</v>
       </c>
       <c r="F41">
-        <v>-8.4583209575569362E-2</v>
+        <v>-0.09083468429934198</v>
       </c>
       <c r="G41">
-        <v>-3.1532002108427E-2</v>
+        <v>-0.03910743668687505</v>
       </c>
       <c r="H41">
-        <v>7.1826565650381577E-2</v>
+        <v>0.05673137510353959</v>
       </c>
       <c r="I41">
-        <v>0.1042207110481712</v>
+        <v>0.09344685230918105</v>
       </c>
       <c r="J41">
-        <v>9.3007234065256822E-2</v>
+        <v>0.08805539735379699</v>
       </c>
       <c r="K41">
-        <v>9.0541193106579307E-2</v>
+        <v>0.09597523839040595</v>
       </c>
       <c r="L41">
-        <v>7.7627622998689708E-2</v>
+        <v>0.07856245089623937</v>
       </c>
       <c r="M41">
-        <v>2.965607220594849E-2</v>
+        <v>0.03635912311581341</v>
       </c>
       <c r="N41">
-        <v>5.4503961190659131E-2</v>
+        <v>0.05804176653357994</v>
       </c>
       <c r="O41">
-        <v>5.4331565102264438E-2</v>
+        <v>0.06104655999312882</v>
       </c>
       <c r="P41">
-        <v>5.2293216882228273E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.06051774178649963</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-8.692012314856748E-2</v>
+        <v>-0.08440044907419667</v>
       </c>
       <c r="C42">
-        <v>-0.17514793086564959</v>
+        <v>-0.1675190824107607</v>
       </c>
       <c r="D42">
-        <v>-0.1476908099562585</v>
+        <v>-0.1398854879172394</v>
       </c>
       <c r="E42">
-        <v>-5.2070438510399986E-3</v>
+        <v>0.00692453690087527</v>
       </c>
       <c r="F42">
-        <v>1.938054528788747E-2</v>
+        <v>0.02751265382431337</v>
       </c>
       <c r="G42">
-        <v>0.15049210929831311</v>
+        <v>0.1520614114160024</v>
       </c>
       <c r="H42">
-        <v>0.28303291832374861</v>
+        <v>0.2694625255723068</v>
       </c>
       <c r="I42">
-        <v>0.27351254987234469</v>
+        <v>0.2674576804399398</v>
       </c>
       <c r="J42">
-        <v>0.23050364964789241</v>
+        <v>0.2262830983381858</v>
       </c>
       <c r="K42">
-        <v>0.1889657084048709</v>
+        <v>0.182329053233986</v>
       </c>
       <c r="L42">
-        <v>0.18734460625461671</v>
+        <v>0.1772643719741785</v>
       </c>
       <c r="M42">
-        <v>0.17114875644895999</v>
+        <v>0.1641928142385302</v>
       </c>
       <c r="N42">
-        <v>0.188272211493236</v>
+        <v>0.1722982993747066</v>
       </c>
       <c r="O42">
-        <v>0.2054830966174778</v>
+        <v>0.191339176233025</v>
       </c>
       <c r="P42">
-        <v>0.21469541546442311</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.20324972746184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-8.1965358069684344E-2</v>
+        <v>-0.08597604976404595</v>
       </c>
       <c r="C43">
-        <v>-0.15676765135220261</v>
+        <v>-0.1546324534342996</v>
       </c>
       <c r="D43">
-        <v>-0.1198096087468852</v>
+        <v>-0.1149410956345632</v>
       </c>
       <c r="E43">
-        <v>5.574202694628932E-3</v>
+        <v>-0.0008803011178764366</v>
       </c>
       <c r="F43">
-        <v>1.1065210512280561E-2</v>
+        <v>0.00996190530208178</v>
       </c>
       <c r="G43">
-        <v>0.1143779180948413</v>
+        <v>0.1131506245529324</v>
       </c>
       <c r="H43">
-        <v>0.24630952414686719</v>
+        <v>0.2462991809072786</v>
       </c>
       <c r="I43">
-        <v>0.23778849038360811</v>
+        <v>0.2382626887641737</v>
       </c>
       <c r="J43">
-        <v>0.24980537117541951</v>
+        <v>0.2452430414473566</v>
       </c>
       <c r="K43">
-        <v>0.24660276435767961</v>
+        <v>0.2361838302333045</v>
       </c>
       <c r="L43">
-        <v>0.22648334599610909</v>
+        <v>0.2284034506572804</v>
       </c>
       <c r="M43">
-        <v>0.25101964973406787</v>
+        <v>0.2445248373235854</v>
       </c>
       <c r="N43">
-        <v>0.23247145322767329</v>
+        <v>0.2331139510721605</v>
       </c>
       <c r="O43">
-        <v>0.21425827609959411</v>
+        <v>0.2150877334648108</v>
       </c>
       <c r="P43">
-        <v>0.21093991723883521</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.2208504471999504</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>-0.114355928774692</v>
+        <v>-0.1166150191957296</v>
       </c>
       <c r="C44">
-        <v>-8.1198481301916578E-2</v>
+        <v>-0.08568569649923771</v>
       </c>
       <c r="D44">
-        <v>5.9036140510248664E-3</v>
+        <v>0.004241334884028187</v>
       </c>
       <c r="E44">
-        <v>-2.5931875296326769E-2</v>
+        <v>-0.02672946074656941</v>
       </c>
       <c r="F44">
-        <v>9.8388051525612669E-2</v>
+        <v>0.09349631760754616</v>
       </c>
       <c r="G44">
-        <v>0.14698683615652999</v>
+        <v>0.1589402298102576</v>
       </c>
       <c r="H44">
-        <v>0.15322012786844719</v>
+        <v>0.1531402466899255</v>
       </c>
       <c r="I44">
-        <v>0.11657616686614709</v>
+        <v>0.1142779581220505</v>
       </c>
       <c r="J44">
-        <v>0.10802087406980659</v>
+        <v>0.1091444274164673</v>
       </c>
       <c r="K44">
-        <v>0.14705551020031449</v>
+        <v>0.1454036879137126</v>
       </c>
       <c r="L44">
-        <v>0.13790216490475271</v>
+        <v>0.1345505032154251</v>
       </c>
       <c r="M44">
-        <v>0.15322792511473959</v>
+        <v>0.1491375208018433</v>
       </c>
       <c r="N44">
-        <v>0.13190486735061741</v>
+        <v>0.1305526886593856</v>
       </c>
       <c r="O44">
-        <v>9.8848986057550853E-2</v>
+        <v>0.1014556306136801</v>
       </c>
       <c r="P44">
-        <v>3.7298390643860563E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.04702939450096773</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>-0.11455059104099791</v>
+        <v>-0.1168745423532851</v>
       </c>
       <c r="C45">
-        <v>-0.27389672700727707</v>
+        <v>-0.2878704572774627</v>
       </c>
       <c r="D45">
-        <v>-0.1794029215090541</v>
+        <v>-0.187799904839801</v>
       </c>
       <c r="E45">
-        <v>-0.18391333226044199</v>
+        <v>-0.1827139760012107</v>
       </c>
       <c r="F45">
-        <v>-0.1068309625778677</v>
+        <v>-0.1094907254695904</v>
       </c>
       <c r="G45">
-        <v>-8.6337081547349578E-2</v>
+        <v>-0.08701596080538532</v>
       </c>
       <c r="H45">
-        <v>-6.4081798394514874E-2</v>
+        <v>-0.06740292888462764</v>
       </c>
       <c r="I45">
-        <v>-1.833153221720462E-2</v>
+        <v>-0.0220511961196147</v>
       </c>
       <c r="J45">
-        <v>-5.2342140001116769E-2</v>
+        <v>-0.04786607318354291</v>
       </c>
       <c r="K45">
-        <v>-7.9856798446709107E-2</v>
+        <v>-0.08034205116146197</v>
       </c>
       <c r="L45">
-        <v>-8.7360068651246472E-2</v>
+        <v>-0.07656221969087972</v>
       </c>
       <c r="M45">
-        <v>-0.1062242573340194</v>
+        <v>-0.09775330883981496</v>
       </c>
       <c r="N45">
-        <v>-0.1599270010312267</v>
+        <v>-0.1516917517577817</v>
       </c>
       <c r="O45">
-        <v>-0.1669874479529844</v>
+        <v>-0.1604993568501385</v>
       </c>
       <c r="P45">
-        <v>-0.18111218046440569</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>-0.180704494734979</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>-1.861109764116263E-2</v>
+        <v>-0.01943771833120427</v>
       </c>
       <c r="C46">
-        <v>-0.29658702280945598</v>
+        <v>-0.299451301671645</v>
       </c>
       <c r="D46">
-        <v>-0.16148749398878501</v>
+        <v>-0.1637327707003554</v>
       </c>
       <c r="E46">
-        <v>5.6416766998787532E-2</v>
+        <v>0.06748415787772552</v>
       </c>
       <c r="F46">
-        <v>0.12510389259787419</v>
+        <v>0.1315146608101442</v>
       </c>
       <c r="G46">
-        <v>0.18087146742805771</v>
+        <v>0.1766658110622349</v>
       </c>
       <c r="H46">
-        <v>0.25916671182619411</v>
+        <v>0.261042633687149</v>
       </c>
       <c r="I46">
-        <v>0.26443071739843083</v>
+        <v>0.2687420795085405</v>
       </c>
       <c r="J46">
-        <v>0.25586608524368509</v>
+        <v>0.2531381398036313</v>
       </c>
       <c r="K46">
-        <v>0.28182561817991347</v>
+        <v>0.2746311490115388</v>
       </c>
       <c r="L46">
-        <v>0.27927574570004088</v>
+        <v>0.2689749068005968</v>
       </c>
       <c r="M46">
-        <v>0.25875808761239433</v>
+        <v>0.2480267432609486</v>
       </c>
       <c r="N46">
-        <v>0.25568669586002962</v>
+        <v>0.243573162467696</v>
       </c>
       <c r="O46">
-        <v>0.25342088058503942</v>
+        <v>0.2436665003420025</v>
       </c>
       <c r="P46">
-        <v>0.23787187828625281</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.2261691810490173</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>-6.6809958973357994E-2</v>
+        <v>-0.07951112901220371</v>
       </c>
       <c r="C47">
-        <v>-0.1111874509763436</v>
+        <v>-0.1261401422125008</v>
       </c>
       <c r="D47">
-        <v>-1.597629522826206E-2</v>
+        <v>-0.02653928998160474</v>
       </c>
       <c r="E47">
-        <v>2.2687743368239189E-2</v>
+        <v>0.005104004100517</v>
       </c>
       <c r="F47">
-        <v>0.17224138686794041</v>
+        <v>0.1722873209920882</v>
       </c>
       <c r="G47">
-        <v>0.22809434415313981</v>
+        <v>0.21971059705037</v>
       </c>
       <c r="H47">
-        <v>0.25927647342324872</v>
+        <v>0.2591090234908717</v>
       </c>
       <c r="I47">
-        <v>0.25406266323812349</v>
+        <v>0.2463352691423425</v>
       </c>
       <c r="J47">
-        <v>0.22012616070430591</v>
+        <v>0.2146271440582259</v>
       </c>
       <c r="K47">
-        <v>0.25302957139816978</v>
+        <v>0.248397337859013</v>
       </c>
       <c r="L47">
-        <v>0.25898232435942309</v>
+        <v>0.2491990064580432</v>
       </c>
       <c r="M47">
-        <v>0.26198322426754711</v>
+        <v>0.2495246518748516</v>
       </c>
       <c r="N47">
-        <v>0.24112050233856661</v>
+        <v>0.2274615478490895</v>
       </c>
       <c r="O47">
-        <v>0.22123429960620369</v>
+        <v>0.2108466063230614</v>
       </c>
       <c r="P47">
-        <v>0.20136344676165799</v>
+        <v>0.1858888790251586</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P19 B21:P47 B20:O20">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_ADJR2.xlsx
@@ -1,21 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV0_ADJR2</t>
+  </si>
+  <si>
+    <t>LV1_ADJR2</t>
+  </si>
+  <si>
+    <t>LV2_ADJR2</t>
+  </si>
+  <si>
+    <t>LV3_ADJR2</t>
+  </si>
+  <si>
+    <t>LV4_ADJR2</t>
+  </si>
+  <si>
+    <t>LV5_ADJR2</t>
+  </si>
+  <si>
+    <t>LV6_ADJR2</t>
+  </si>
+  <si>
+    <t>LV7_ADJR2</t>
+  </si>
+  <si>
+    <t>LV8_ADJR2</t>
+  </si>
+  <si>
+    <t>LV9_ADJR2</t>
+  </si>
+  <si>
+    <t>LV10_ADJR2</t>
+  </si>
+  <si>
+    <t>LV11_ADJR2</t>
+  </si>
+  <si>
+    <t>LV12_ADJR2</t>
+  </si>
+  <si>
+    <t>LV13_ADJR2</t>
+  </si>
+  <si>
+    <t>LV14_ADJR2</t>
+  </si>
+  <si>
+    <t>LV15_ADJR2</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -40,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -48,26 +235,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +351,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +383,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +418,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +594,2310 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_ADJR2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_ADJR2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_ADJR2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_ADJR2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_ADJR2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_ADJR2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_ADJR2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_ADJR2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_ADJR2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_ADJR2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_ADJR2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_ADJR2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_ADJR2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_ADJR2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_ADJR2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>-0.05290805228241287</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C2">
-        <v>-0.09443372468019956</v>
+        <v>-5.2550455621270413E-2</v>
       </c>
       <c r="D2">
-        <v>-0.09126380938006122</v>
+        <v>-9.7262612983411975E-2</v>
       </c>
       <c r="E2">
-        <v>-0.07399877926477889</v>
+        <v>-8.8943127082720327E-2</v>
       </c>
       <c r="F2">
-        <v>-0.09241042489189458</v>
+        <v>-6.9106367497370189E-2</v>
       </c>
       <c r="G2">
-        <v>-0.09754132334002055</v>
+        <v>-9.2374790880846325E-2</v>
       </c>
       <c r="H2">
-        <v>-0.03574552227493144</v>
+        <v>-9.0760157505488548E-2</v>
       </c>
       <c r="I2">
-        <v>0.02164721650338612</v>
+        <v>-3.121954025894625E-2</v>
       </c>
       <c r="J2">
-        <v>-0.01506384052866705</v>
+        <v>2.457360742735135E-2</v>
       </c>
       <c r="K2">
-        <v>0.02926372003213413</v>
+        <v>-2.88328434776596E-3</v>
       </c>
       <c r="L2">
-        <v>0.1126649665114981</v>
+        <v>4.0909238273259103E-2</v>
       </c>
       <c r="M2">
-        <v>0.1431542778907414</v>
+        <v>0.1228394107623119</v>
       </c>
       <c r="N2">
-        <v>0.2506907001058473</v>
-      </c>
-      <c r="O2">
-        <v>0.337638069859681</v>
+        <v>0.14771589886262829</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.25209421445845759</v>
       </c>
       <c r="P2">
-        <v>0.3788698974968241</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.34383847846306032</v>
+      </c>
+      <c r="Q2">
+        <v>0.38130390027101418</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>-0.02338977500364613</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C3">
-        <v>-0.2005140104515763</v>
+        <v>-2.520547656425379E-2</v>
       </c>
       <c r="D3">
-        <v>-0.1336381738029375</v>
+        <v>-0.20794065501162759</v>
       </c>
       <c r="E3">
-        <v>0.01189838638913474</v>
+        <v>-0.14325961226426781</v>
       </c>
       <c r="F3">
-        <v>0.096576438331663</v>
+        <v>9.086766115276132E-3</v>
       </c>
       <c r="G3">
-        <v>0.15034460181354</v>
+        <v>9.9040304141408228E-2</v>
       </c>
       <c r="H3">
-        <v>0.2068370342305458</v>
-      </c>
-      <c r="I3">
-        <v>0.2308688696167037</v>
+        <v>0.1476116495900314</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.20435468726528189</v>
       </c>
       <c r="J3">
-        <v>0.2770922267672325</v>
+        <v>0.23349003287455419</v>
       </c>
       <c r="K3">
-        <v>0.3085641985620685</v>
+        <v>0.28105071595194159</v>
       </c>
       <c r="L3">
-        <v>0.3038172183834741</v>
+        <v>0.30996570516911381</v>
       </c>
       <c r="M3">
-        <v>0.3001693282739456</v>
+        <v>0.30192263969268091</v>
       </c>
       <c r="N3">
-        <v>0.2718381996675007</v>
+        <v>0.29543928794617891</v>
       </c>
       <c r="O3">
-        <v>0.2618310565870506</v>
+        <v>0.2736782547501706</v>
       </c>
       <c r="P3">
-        <v>0.2795035035171569</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.25842696411123139</v>
+      </c>
+      <c r="Q3">
+        <v>0.27991452256752147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>-0.0428466917420348</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C4">
-        <v>-0.06111144707903773</v>
+        <v>-4.5362881162091188E-2</v>
       </c>
       <c r="D4">
-        <v>-0.1360344163531771</v>
+        <v>-6.770439059669639E-2</v>
       </c>
       <c r="E4">
-        <v>-0.1330592574692104</v>
+        <v>-0.14118532739277351</v>
       </c>
       <c r="F4">
-        <v>-0.190699294789714</v>
+        <v>-0.14990509074341299</v>
       </c>
       <c r="G4">
-        <v>-0.08282408736231285</v>
+        <v>-0.21003954240716219</v>
       </c>
       <c r="H4">
-        <v>0.01328630784015376</v>
+        <v>-8.1316683024048222E-2</v>
       </c>
       <c r="I4">
-        <v>0.05917543654447926</v>
+        <v>3.8107845748587549E-4</v>
       </c>
       <c r="J4">
-        <v>0.06003981550784616</v>
+        <v>4.5464768026364809E-2</v>
       </c>
       <c r="K4">
-        <v>0.128891342948196</v>
+        <v>5.6033882293843373E-2</v>
       </c>
       <c r="L4">
-        <v>0.203927389445575</v>
-      </c>
-      <c r="M4">
-        <v>0.2686259895627416</v>
+        <v>0.12524095833079679</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.20040786683933079</v>
       </c>
       <c r="N4">
-        <v>0.3006960808422861</v>
+        <v>0.25918862700745299</v>
       </c>
       <c r="O4">
-        <v>0.3044819192176804</v>
+        <v>0.29492491710344348</v>
       </c>
       <c r="P4">
-        <v>0.2883521766904619</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.29557952089133449</v>
+      </c>
+      <c r="Q4">
+        <v>0.27928754637975339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>-0.03312243053805321</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C5">
-        <v>-0.1079856605714667</v>
+        <v>-3.6196279957058972E-2</v>
       </c>
       <c r="D5">
-        <v>-0.05459503733835095</v>
+        <v>-0.1034457650343157</v>
       </c>
       <c r="E5">
-        <v>-0.1533703686752587</v>
+        <v>-5.3856692236063528E-2</v>
       </c>
       <c r="F5">
-        <v>0.04500865097458337</v>
+        <v>-0.146869735741334</v>
       </c>
       <c r="G5">
-        <v>0.140069127099583</v>
+        <v>4.6525633420117493E-2</v>
       </c>
       <c r="H5">
-        <v>0.1693533787621279</v>
+        <v>0.1355329518759654</v>
       </c>
       <c r="I5">
-        <v>0.2433539035224792</v>
+        <v>0.18098017188891349</v>
       </c>
       <c r="J5">
-        <v>0.3180588361562025</v>
-      </c>
-      <c r="K5">
-        <v>0.3489745368898846</v>
+        <v>0.25303828014880841</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.32566059395220498</v>
       </c>
       <c r="L5">
-        <v>0.3763020465304756</v>
+        <v>0.35412591642843461</v>
       </c>
       <c r="M5">
-        <v>0.3728807720822168</v>
+        <v>0.38514256997671148</v>
       </c>
       <c r="N5">
-        <v>0.3450381085123028</v>
+        <v>0.38662542466574967</v>
       </c>
       <c r="O5">
-        <v>0.3228496262300381</v>
+        <v>0.36037627327054722</v>
       </c>
       <c r="P5">
-        <v>0.2982882160189976</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.34411208266266641</v>
+      </c>
+      <c r="Q5">
+        <v>0.31896084964283228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>-0.04125468019205144</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C6">
-        <v>-0.1260005161593283</v>
+        <v>-3.8196498543364168E-2</v>
       </c>
       <c r="D6">
-        <v>-0.07472468280652299</v>
+        <v>-0.1283806882142659</v>
       </c>
       <c r="E6">
-        <v>-0.1059164955041367</v>
+        <v>-8.111162612341738E-2</v>
       </c>
       <c r="F6">
-        <v>0.1220747841336962</v>
+        <v>-0.1133309657243551</v>
       </c>
       <c r="G6">
-        <v>0.2161262494102473</v>
+        <v>0.1072755543189112</v>
       </c>
       <c r="H6">
-        <v>0.2746259590753149</v>
+        <v>0.2099322515226103</v>
       </c>
       <c r="I6">
-        <v>0.3459763203635747</v>
-      </c>
-      <c r="J6">
-        <v>0.3881054825802105</v>
+        <v>0.26266255994205479</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.34480566961040682</v>
       </c>
       <c r="K6">
-        <v>0.4035709836089363</v>
+        <v>0.3836101171600404</v>
       </c>
       <c r="L6">
-        <v>0.4237128868756384</v>
+        <v>0.39448610989078031</v>
       </c>
       <c r="M6">
-        <v>0.423067537669095</v>
+        <v>0.41465166640704532</v>
       </c>
       <c r="N6">
-        <v>0.4141939030950985</v>
+        <v>0.42169368994676909</v>
       </c>
       <c r="O6">
-        <v>0.4177925070200633</v>
+        <v>0.41111007261017052</v>
       </c>
       <c r="P6">
-        <v>0.3980682099023359</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.41788249925015619</v>
+      </c>
+      <c r="Q6">
+        <v>0.39590815387857031</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-0.04909751690350871</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C7">
-        <v>-0.0736802005837856</v>
+        <v>-4.623755128213497E-2</v>
       </c>
       <c r="D7">
-        <v>-0.1418812321450353</v>
+        <v>-6.9633730633971963E-2</v>
       </c>
       <c r="E7">
-        <v>-0.166917769578189</v>
+        <v>-0.13723371920790839</v>
       </c>
       <c r="F7">
-        <v>-0.2299105953192488</v>
+        <v>-0.16144648933783401</v>
       </c>
       <c r="G7">
-        <v>-0.1833269736810698</v>
+        <v>-0.23232668064604359</v>
       </c>
       <c r="H7">
-        <v>-0.06090437602934785</v>
+        <v>-0.17633914031345341</v>
       </c>
       <c r="I7">
-        <v>0.03096514335234943</v>
+        <v>-6.5106042751975027E-2</v>
       </c>
       <c r="J7">
-        <v>0.05937293358241083</v>
+        <v>3.2541317110493038E-2</v>
       </c>
       <c r="K7">
-        <v>0.07702919702022842</v>
+        <v>5.9119869551080943E-2</v>
       </c>
       <c r="L7">
-        <v>0.1663863395715357</v>
+        <v>7.2107725656528135E-2</v>
       </c>
       <c r="M7">
-        <v>0.2416368530020362</v>
-      </c>
-      <c r="N7">
-        <v>0.2913360647965418</v>
+        <v>0.17740569904209849</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.24849207217568531</v>
       </c>
       <c r="O7">
-        <v>0.3198451662837481</v>
+        <v>0.3060363177200251</v>
       </c>
       <c r="P7">
-        <v>0.324847176752883</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.32929436217281483</v>
+      </c>
+      <c r="Q7">
+        <v>0.33328488692686392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>-0.04161676453248285</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C8">
-        <v>-0.07057973858627373</v>
+        <v>-4.2673853363968423E-2</v>
       </c>
       <c r="D8">
-        <v>-0.1416418503408551</v>
+        <v>-7.3376073367082864E-2</v>
       </c>
       <c r="E8">
-        <v>-0.1841140903868618</v>
+        <v>-0.1459922276099366</v>
       </c>
       <c r="F8">
-        <v>-0.116649992358776</v>
+        <v>-0.19586100180913379</v>
       </c>
       <c r="G8">
-        <v>-0.01159558520438136</v>
+        <v>-0.126923973801981</v>
       </c>
       <c r="H8">
-        <v>0.002520041407645481</v>
+        <v>-1.904248483229137E-2</v>
       </c>
       <c r="I8">
-        <v>0.1065358913817622</v>
+        <v>-2.2355301947548801E-3</v>
       </c>
       <c r="J8">
-        <v>0.144366519885698</v>
+        <v>0.1029725941298978</v>
       </c>
       <c r="K8">
-        <v>0.2649601125690919</v>
-      </c>
-      <c r="L8">
-        <v>0.28527948609592</v>
+        <v>0.14863820911505479</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.26460285858376043</v>
       </c>
       <c r="M8">
-        <v>0.3309250211665592</v>
+        <v>0.28160962104249609</v>
       </c>
       <c r="N8">
-        <v>0.3553589923148681</v>
+        <v>0.32346500604366318</v>
       </c>
       <c r="O8">
-        <v>0.3554175993741481</v>
+        <v>0.34783089545000517</v>
       </c>
       <c r="P8">
-        <v>0.3380462752054365</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.3475324971200453</v>
+      </c>
+      <c r="Q8">
+        <v>0.33539573160720548</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>-0.03607211251945661</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C9">
-        <v>-0.06618608712226516</v>
+        <v>-3.9285169840428992E-2</v>
       </c>
       <c r="D9">
-        <v>-0.1340323915188795</v>
+        <v>-6.3087191800144285E-2</v>
       </c>
       <c r="E9">
-        <v>-0.1582107314652125</v>
+        <v>-0.13102076231499249</v>
       </c>
       <c r="F9">
-        <v>-0.1084794204748158</v>
+        <v>-0.16219552552984851</v>
       </c>
       <c r="G9">
-        <v>-0.002529489497045507</v>
+        <v>-0.1121480774895057</v>
       </c>
       <c r="H9">
-        <v>0.01234063892225965</v>
+        <v>-7.6805907088194946E-3</v>
       </c>
       <c r="I9">
-        <v>0.1110449185537352</v>
+        <v>4.2001986300394421E-3</v>
       </c>
       <c r="J9">
-        <v>0.1419693006268327</v>
+        <v>0.10493091618121191</v>
       </c>
       <c r="K9">
-        <v>0.2950826625093015</v>
-      </c>
-      <c r="L9">
-        <v>0.2914990300899697</v>
+        <v>0.13483337434169429</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.28961142760915748</v>
       </c>
       <c r="M9">
-        <v>0.3361571278411461</v>
+        <v>0.28161941890949738</v>
       </c>
       <c r="N9">
-        <v>0.3652434933016384</v>
+        <v>0.32754532377898388</v>
       </c>
       <c r="O9">
-        <v>0.3584917404340702</v>
+        <v>0.35574802544189782</v>
       </c>
       <c r="P9">
-        <v>0.3574368941203669</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.35180341579378138</v>
+      </c>
+      <c r="Q9">
+        <v>0.34988188635983603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>-0.04436179603757926</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C10">
-        <v>-0.06975792298954123</v>
+        <v>-4.1779834522308303E-2</v>
       </c>
       <c r="D10">
-        <v>-0.1358701835681858</v>
+        <v>-7.3127840685657808E-2</v>
       </c>
       <c r="E10">
-        <v>-0.1686031173526272</v>
+        <v>-0.13886532314941949</v>
       </c>
       <c r="F10">
-        <v>-0.1147508276794303</v>
+        <v>-0.16490607969977239</v>
       </c>
       <c r="G10">
-        <v>-0.01438681787367518</v>
+        <v>-0.1133516710871387</v>
       </c>
       <c r="H10">
-        <v>0.00764717993509962</v>
+        <v>-6.0015388342727748E-3</v>
       </c>
       <c r="I10">
-        <v>0.1005976557766696</v>
+        <v>7.2144518880046882E-3</v>
       </c>
       <c r="J10">
-        <v>0.1275128425245546</v>
+        <v>0.1066167670939992</v>
       </c>
       <c r="K10">
-        <v>0.2922363191494189</v>
-      </c>
-      <c r="L10">
-        <v>0.2738511236655066</v>
+        <v>0.14187817889841511</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.29097238532242858</v>
       </c>
       <c r="M10">
-        <v>0.319100694959749</v>
+        <v>0.27886399032473869</v>
       </c>
       <c r="N10">
-        <v>0.3520255984220858</v>
+        <v>0.32266084205467799</v>
       </c>
       <c r="O10">
-        <v>0.3425410242127483</v>
+        <v>0.34904949561936821</v>
       </c>
       <c r="P10">
-        <v>0.3450864745727105</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.34034208471476141</v>
+      </c>
+      <c r="Q10">
+        <v>0.33578147406989273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>-0.03969628540689531</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C11">
-        <v>-0.07027569620302601</v>
+        <v>-3.8685697977049002E-2</v>
       </c>
       <c r="D11">
-        <v>-0.1420095071475114</v>
+        <v>-6.8394876199665278E-2</v>
       </c>
       <c r="E11">
-        <v>-0.1789542672539678</v>
+        <v>-0.13439265531976141</v>
       </c>
       <c r="F11">
-        <v>-0.1265133851181932</v>
+        <v>-0.16539713944553661</v>
       </c>
       <c r="G11">
-        <v>-0.01177472964020464</v>
+        <v>-0.11469064085100091</v>
       </c>
       <c r="H11">
-        <v>-0.006069604479411798</v>
+        <v>-1.0331245414816869E-2</v>
       </c>
       <c r="I11">
-        <v>0.1025672093117999</v>
+        <v>-3.708819364246144E-3</v>
       </c>
       <c r="J11">
-        <v>0.1346634198528251</v>
+        <v>9.5693243121426144E-2</v>
       </c>
       <c r="K11">
-        <v>0.2911464398552266</v>
-      </c>
-      <c r="L11">
-        <v>0.2935264437604828</v>
+        <v>0.1218998373463319</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.27736340438627771</v>
       </c>
       <c r="M11">
-        <v>0.3355304121454212</v>
+        <v>0.28067446199123858</v>
       </c>
       <c r="N11">
-        <v>0.3584664162819911</v>
+        <v>0.32740179356263022</v>
       </c>
       <c r="O11">
-        <v>0.3547477660320685</v>
+        <v>0.35578450654795929</v>
       </c>
       <c r="P11">
-        <v>0.3515386512891109</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.34849370378270222</v>
+      </c>
+      <c r="Q11">
+        <v>0.34759086815231671</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>-0.0346307935781022</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C12">
-        <v>-0.1078839043058303</v>
+        <v>-3.07377212545616E-2</v>
       </c>
       <c r="D12">
-        <v>-0.05417091129565035</v>
+        <v>-9.8122392847992582E-2</v>
       </c>
       <c r="E12">
-        <v>-0.1577660157634832</v>
+        <v>-6.0318999109531903E-2</v>
       </c>
       <c r="F12">
-        <v>0.02697042290836292</v>
+        <v>-0.15043543431820011</v>
       </c>
       <c r="G12">
-        <v>0.09240585211540434</v>
+        <v>4.029505779682914E-2</v>
       </c>
       <c r="H12">
-        <v>0.2017873445031116</v>
+        <v>9.4786450481839785E-2</v>
       </c>
       <c r="I12">
-        <v>0.3139854298249561</v>
+        <v>0.21260154222858349</v>
       </c>
       <c r="J12">
-        <v>0.3752649026421077</v>
-      </c>
-      <c r="K12">
-        <v>0.4056492773492206</v>
+        <v>0.31127945018260228</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.37009438443267861</v>
       </c>
       <c r="L12">
-        <v>0.4381332842070348</v>
+        <v>0.39678182717370369</v>
       </c>
       <c r="M12">
-        <v>0.4418204208437043</v>
+        <v>0.42460790941895121</v>
       </c>
       <c r="N12">
-        <v>0.4232338586271512</v>
+        <v>0.42744942495337668</v>
       </c>
       <c r="O12">
-        <v>0.4008036707787858</v>
+        <v>0.40381215071444931</v>
       </c>
       <c r="P12">
-        <v>0.3663172775784367</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.37888161671188447</v>
+      </c>
+      <c r="Q12">
+        <v>0.3322910541705979</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>-0.04913895576458743</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C13">
-        <v>-0.1894446586768078</v>
+        <v>-4.474374794869912E-2</v>
       </c>
       <c r="D13">
-        <v>-0.1083141069980394</v>
+        <v>-0.18722925589868869</v>
       </c>
       <c r="E13">
-        <v>-0.1631794853789215</v>
+        <v>-0.1190689446765482</v>
       </c>
       <c r="F13">
-        <v>-0.1526732075581595</v>
+        <v>-0.17176007684116509</v>
       </c>
       <c r="G13">
-        <v>-0.008121960627004311</v>
+        <v>-0.16188475811797801</v>
       </c>
       <c r="H13">
-        <v>-0.004027723758630037</v>
+        <v>-1.039567584252598E-2</v>
       </c>
       <c r="I13">
-        <v>0.04656211036215092</v>
+        <v>-8.0430393550000694E-3</v>
       </c>
       <c r="J13">
-        <v>0.1196291661391424</v>
-      </c>
-      <c r="K13">
-        <v>0.1998711389252364</v>
+        <v>4.2226140852033793E-2</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.12680739422929521</v>
       </c>
       <c r="L13">
-        <v>0.2088850523414892</v>
+        <v>0.20353410465515209</v>
       </c>
       <c r="M13">
-        <v>0.2319156624246561</v>
+        <v>0.21531714394567469</v>
       </c>
       <c r="N13">
-        <v>0.2378089985964852</v>
+        <v>0.24917624610613559</v>
       </c>
       <c r="O13">
-        <v>0.2551540197076286</v>
+        <v>0.24961161216950301</v>
       </c>
       <c r="P13">
-        <v>0.2482487881448251</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.26830841625161772</v>
+      </c>
+      <c r="Q13">
+        <v>0.2553426943076092</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>-0.04808359499714973</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C14">
-        <v>-0.06989451551362991</v>
+        <v>-4.8530708546551497E-2</v>
       </c>
       <c r="D14">
-        <v>-0.1359592397017341</v>
+        <v>-7.0860743443451946E-2</v>
       </c>
       <c r="E14">
-        <v>-0.1530254182300488</v>
+        <v>-0.1362511767694711</v>
       </c>
       <c r="F14">
-        <v>-0.2184645555625079</v>
+        <v>-0.14926044016438519</v>
       </c>
       <c r="G14">
-        <v>-0.1691453372634291</v>
+        <v>-0.2110316110340095</v>
       </c>
       <c r="H14">
-        <v>-0.06452942683433724</v>
+        <v>-0.17213963729386059</v>
       </c>
       <c r="I14">
-        <v>0.02753580605314065</v>
+        <v>-6.0199183800457488E-2</v>
       </c>
       <c r="J14">
-        <v>0.04629384918900526</v>
+        <v>3.4693740368685409E-2</v>
       </c>
       <c r="K14">
-        <v>0.07711068128584031</v>
+        <v>6.5479670574415991E-2</v>
       </c>
       <c r="L14">
-        <v>0.1819680445369364</v>
+        <v>7.7274837896374834E-2</v>
       </c>
       <c r="M14">
-        <v>0.2957630443815166</v>
-      </c>
-      <c r="N14">
-        <v>0.3294373927558529</v>
+        <v>0.18684634558143309</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0.29917290069171609</v>
       </c>
       <c r="O14">
-        <v>0.3582996416016216</v>
+        <v>0.34173342144896152</v>
       </c>
       <c r="P14">
-        <v>0.3841058031065494</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.36844467332926051</v>
+      </c>
+      <c r="Q14">
+        <v>0.38396338506653421</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>-0.05173732756432053</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C15">
-        <v>-0.07387379987922131</v>
+        <v>-4.9973465672468402E-2</v>
       </c>
       <c r="D15">
-        <v>-0.1391800687413293</v>
+        <v>-7.0829884027051912E-2</v>
       </c>
       <c r="E15">
-        <v>-0.1551677339159433</v>
+        <v>-0.13746554426917021</v>
       </c>
       <c r="F15">
-        <v>-0.2207788171001065</v>
+        <v>-0.15591149191897949</v>
       </c>
       <c r="G15">
-        <v>-0.1768674468017013</v>
+        <v>-0.2188626146343019</v>
       </c>
       <c r="H15">
-        <v>-0.06427439069833023</v>
+        <v>-0.16950353681773839</v>
       </c>
       <c r="I15">
-        <v>0.008967489720978421</v>
+        <v>-6.2961323368463162E-2</v>
       </c>
       <c r="J15">
-        <v>0.03554955756247546</v>
+        <v>2.467543644693317E-2</v>
       </c>
       <c r="K15">
-        <v>0.06604659091536209</v>
+        <v>4.5835795891743053E-2</v>
       </c>
       <c r="L15">
-        <v>0.1610332049896538</v>
+        <v>6.3907474188459185E-2</v>
       </c>
       <c r="M15">
-        <v>0.263589153249133</v>
-      </c>
-      <c r="N15">
-        <v>0.3041205993509052</v>
+        <v>0.16147322343166551</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.25752096561330567</v>
       </c>
       <c r="O15">
-        <v>0.3269921843701488</v>
+        <v>0.29927885338507881</v>
       </c>
       <c r="P15">
-        <v>0.3508115932889618</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.32602999475238598</v>
+      </c>
+      <c r="Q15">
+        <v>0.34406009728547932</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>-0.04446687221492027</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C16">
-        <v>-0.0667859988670014</v>
+        <v>-4.3423031325673732E-2</v>
       </c>
       <c r="D16">
-        <v>-0.1330920695925161</v>
+        <v>-6.6219779817027133E-2</v>
       </c>
       <c r="E16">
-        <v>-0.1482428139168927</v>
+        <v>-0.1367475910954758</v>
       </c>
       <c r="F16">
-        <v>-0.2061264177841818</v>
+        <v>-0.15716085490876239</v>
       </c>
       <c r="G16">
-        <v>-0.173022460913709</v>
+        <v>-0.21760505993503071</v>
       </c>
       <c r="H16">
-        <v>-0.0734038769405486</v>
+        <v>-0.18063204050410761</v>
       </c>
       <c r="I16">
-        <v>0.0166553908256214</v>
+        <v>-7.1782090712815189E-2</v>
       </c>
       <c r="J16">
-        <v>0.0475133385834571</v>
+        <v>1.2644273002369991E-2</v>
       </c>
       <c r="K16">
-        <v>0.06818775118554758</v>
+        <v>3.9889185259313703E-2</v>
       </c>
       <c r="L16">
-        <v>0.1548809851226433</v>
+        <v>5.3307695413271503E-2</v>
       </c>
       <c r="M16">
-        <v>0.2613204978487123</v>
-      </c>
-      <c r="N16">
-        <v>0.3093014510542064</v>
+        <v>0.14590876932473901</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.26259066350339078</v>
       </c>
       <c r="O16">
-        <v>0.3427064481324344</v>
+        <v>0.29983502239991039</v>
       </c>
       <c r="P16">
-        <v>0.3609336804059972</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.32945520068508882</v>
+      </c>
+      <c r="Q16">
+        <v>0.35548841210065107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>-0.04572540764015509</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C17">
-        <v>-0.07038254004729763</v>
+        <v>-4.7482754665521328E-2</v>
       </c>
       <c r="D17">
-        <v>-0.1386711192880916</v>
+        <v>-7.1536980033520312E-2</v>
       </c>
       <c r="E17">
-        <v>-0.1568524062136907</v>
+        <v>-0.1374591323891203</v>
       </c>
       <c r="F17">
-        <v>-0.2068771992387269</v>
+        <v>-0.15430375068594679</v>
       </c>
       <c r="G17">
-        <v>-0.1757930834748186</v>
+        <v>-0.2166419079545511</v>
       </c>
       <c r="H17">
-        <v>-0.06828710596107102</v>
+        <v>-0.1745681454940976</v>
       </c>
       <c r="I17">
-        <v>0.02163875727083861</v>
+        <v>-6.8376193726815429E-2</v>
       </c>
       <c r="J17">
-        <v>0.03663451699611057</v>
+        <v>1.221897339123898E-2</v>
       </c>
       <c r="K17">
-        <v>0.05192965616571638</v>
+        <v>3.2465016259714423E-2</v>
       </c>
       <c r="L17">
-        <v>0.1318304182993626</v>
+        <v>4.7377061847419681E-2</v>
       </c>
       <c r="M17">
-        <v>0.2347247332788074</v>
-      </c>
-      <c r="N17">
-        <v>0.2687167490995108</v>
+        <v>0.14108651132804129</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.2382178486985527</v>
       </c>
       <c r="O17">
-        <v>0.3007002963299794</v>
+        <v>0.2727439719867894</v>
       </c>
       <c r="P17">
-        <v>0.3195156908433222</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.30087462320269981</v>
+      </c>
+      <c r="Q17">
+        <v>0.32652272963521312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>-0.03324441172796243</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C18">
-        <v>-0.111873061215821</v>
+        <v>-3.5889921305602507E-2</v>
       </c>
       <c r="D18">
-        <v>-0.05671004413398262</v>
+        <v>-0.107997720390514</v>
       </c>
       <c r="E18">
-        <v>-0.1638915953642512</v>
+        <v>-7.032823334884393E-2</v>
       </c>
       <c r="F18">
-        <v>0.06233836615829323</v>
+        <v>-0.1633927320141832</v>
       </c>
       <c r="G18">
-        <v>0.1398011461922045</v>
+        <v>5.213144688068972E-2</v>
       </c>
       <c r="H18">
-        <v>0.216513369919801</v>
+        <v>0.13112224326239369</v>
       </c>
       <c r="I18">
-        <v>0.3064404133723341</v>
-      </c>
-      <c r="J18">
-        <v>0.3702879597033081</v>
+        <v>0.2028500417623452</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.29625420459944207</v>
       </c>
       <c r="K18">
-        <v>0.3896170179771432</v>
+        <v>0.3681166031989177</v>
       </c>
       <c r="L18">
-        <v>0.4150460230905175</v>
+        <v>0.38499751014153488</v>
       </c>
       <c r="M18">
-        <v>0.4233206098792784</v>
+        <v>0.41289795375256272</v>
       </c>
       <c r="N18">
-        <v>0.3950193390999827</v>
+        <v>0.41309959910558208</v>
       </c>
       <c r="O18">
-        <v>0.3724735410620446</v>
+        <v>0.39085088343456859</v>
       </c>
       <c r="P18">
-        <v>0.3512037421869109</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.36249942283783221</v>
+      </c>
+      <c r="Q18">
+        <v>0.34565935760167638</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>-0.03747800578326009</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C19">
-        <v>-0.1391249362925348</v>
+        <v>-4.0152214407044577E-2</v>
       </c>
       <c r="D19">
-        <v>-0.09751963475036277</v>
+        <v>-0.1318489393411055</v>
       </c>
       <c r="E19">
-        <v>-0.1485559962969979</v>
+        <v>-7.7953506864173655E-2</v>
       </c>
       <c r="F19">
-        <v>0.1110496794115069</v>
+        <v>-0.1316819857062777</v>
       </c>
       <c r="G19">
-        <v>0.1955476426615595</v>
+        <v>0.1304797477702134</v>
       </c>
       <c r="H19">
-        <v>0.2696519303855587</v>
+        <v>0.19349662701618431</v>
       </c>
       <c r="I19">
-        <v>0.3502012457951504</v>
-      </c>
-      <c r="J19">
-        <v>0.3964427780747922</v>
-      </c>
-      <c r="K19">
-        <v>0.4092652347595571</v>
+        <v>0.26216180398487399</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0.3444855488388131</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.39745030032694773</v>
       </c>
       <c r="L19">
-        <v>0.4322564284528748</v>
+        <v>0.41453804956747242</v>
       </c>
       <c r="M19">
-        <v>0.4346961299285406</v>
+        <v>0.43850863249032529</v>
       </c>
       <c r="N19">
-        <v>0.427781846224992</v>
+        <v>0.43873406264921089</v>
       </c>
       <c r="O19">
-        <v>0.4293157470341714</v>
+        <v>0.42773025395201991</v>
       </c>
       <c r="P19">
-        <v>0.4167370986831487</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.43068483663476631</v>
+      </c>
+      <c r="Q19">
+        <v>0.41881900010929829</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>-0.03691273779090799</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C20">
-        <v>-0.1470038550428454</v>
+        <v>-3.5195636678893999E-2</v>
       </c>
       <c r="D20">
-        <v>-0.1084806214982055</v>
+        <v>-0.13957264672104069</v>
       </c>
       <c r="E20">
-        <v>-0.01817334624716842</v>
+        <v>-0.1028179769966806</v>
       </c>
       <c r="F20">
-        <v>0.0913296051771481</v>
+        <v>-1.1712305497346739E-2</v>
       </c>
       <c r="G20">
-        <v>0.1161355191973047</v>
+        <v>0.1000906487641019</v>
       </c>
       <c r="H20">
-        <v>0.213492732844479</v>
+        <v>0.13931036853648829</v>
       </c>
       <c r="I20">
-        <v>0.2985283521661847</v>
-      </c>
-      <c r="J20">
-        <v>0.340126685116913</v>
-      </c>
-      <c r="K20">
-        <v>0.3844635314955261</v>
+        <v>0.23023520396283889</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.31294985561472238</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.3503563973926313</v>
       </c>
       <c r="L20">
-        <v>0.3931755789314698</v>
+        <v>0.39472920756052088</v>
       </c>
       <c r="M20">
-        <v>0.397289770629951</v>
+        <v>0.39644249111268132</v>
       </c>
       <c r="N20">
-        <v>0.436570651877731</v>
+        <v>0.39775820783380678</v>
       </c>
       <c r="O20">
-        <v>0.4371537737006477</v>
+        <v>0.44035117134252799</v>
       </c>
       <c r="P20">
-        <v>0.4331722122125706</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.43502267807654932</v>
+      </c>
+      <c r="Q20">
+        <v>0.43177011580709268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>-0.02334707594584575</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C21">
-        <v>-0.1866885854365806</v>
+        <v>-2.4790219582243901E-2</v>
       </c>
       <c r="D21">
-        <v>-0.1348516536432175</v>
+        <v>-0.1908979540637355</v>
       </c>
       <c r="E21">
-        <v>-0.01362758374560174</v>
+        <v>-0.14170754928098181</v>
       </c>
       <c r="F21">
-        <v>0.05189538556187611</v>
+        <v>-4.7074131621359198E-3</v>
       </c>
       <c r="G21">
-        <v>0.08137399859106384</v>
+        <v>6.1399559960686842E-2</v>
       </c>
       <c r="H21">
-        <v>0.1363534809165161</v>
+        <v>9.0542858539730167E-2</v>
       </c>
       <c r="I21">
-        <v>0.1771938216111085</v>
-      </c>
-      <c r="J21">
-        <v>0.2567529391222928</v>
+        <v>0.14736972272451909</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.18994400888017229</v>
       </c>
       <c r="K21">
-        <v>0.2923893779586586</v>
+        <v>0.26514519264281261</v>
       </c>
       <c r="L21">
-        <v>0.3083295716797269</v>
+        <v>0.30042166369818218</v>
       </c>
       <c r="M21">
-        <v>0.2923539091645606</v>
+        <v>0.31538145233595261</v>
       </c>
       <c r="N21">
-        <v>0.2604942805217177</v>
+        <v>0.29693922765172759</v>
       </c>
       <c r="O21">
-        <v>0.2391474668012657</v>
+        <v>0.25344429684264902</v>
       </c>
       <c r="P21">
-        <v>0.2489051300180811</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.2330343164642858</v>
+      </c>
+      <c r="Q21">
+        <v>0.24814010955127991</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>-0.02325415210536807</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C22">
-        <v>-0.1831882922030569</v>
+        <v>-2.0201778673826248E-2</v>
       </c>
       <c r="D22">
-        <v>-0.127459371179816</v>
+        <v>-0.17648996761647651</v>
       </c>
       <c r="E22">
-        <v>0.007992810066180699</v>
+        <v>-0.13012102167370429</v>
       </c>
       <c r="F22">
-        <v>0.06220966402277668</v>
+        <v>5.6077318984133553E-3</v>
       </c>
       <c r="G22">
-        <v>0.08162106584404358</v>
+        <v>5.880395185851095E-2</v>
       </c>
       <c r="H22">
-        <v>0.1098006311829648</v>
+        <v>8.237167958657457E-2</v>
       </c>
       <c r="I22">
-        <v>0.1286881853650335</v>
-      </c>
-      <c r="J22">
-        <v>0.1970431490551278</v>
+        <v>0.1105367611429238</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.12775607113907969</v>
       </c>
       <c r="K22">
-        <v>0.2387557792789213</v>
+        <v>0.20452745430320479</v>
       </c>
       <c r="L22">
-        <v>0.2487954062366606</v>
+        <v>0.24302740772863021</v>
       </c>
       <c r="M22">
-        <v>0.2537606883678764</v>
+        <v>0.25991302266106148</v>
       </c>
       <c r="N22">
-        <v>0.2351152877833492</v>
+        <v>0.26813005296774439</v>
       </c>
       <c r="O22">
-        <v>0.2294834846096991</v>
+        <v>0.25102947173862988</v>
       </c>
       <c r="P22">
-        <v>0.2278860071787831</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.24958067232397629</v>
+      </c>
+      <c r="Q22">
+        <v>0.24950853309087179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>-0.0332648932388941</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C23">
-        <v>-0.1474635156474073</v>
+        <v>-4.1122705976330692E-2</v>
       </c>
       <c r="D23">
-        <v>-0.02314808568866864</v>
+        <v>-0.1536232167025561</v>
       </c>
       <c r="E23">
-        <v>0.07485751941415106</v>
+        <v>-5.0856538421342343E-2</v>
       </c>
       <c r="F23">
-        <v>0.2188420234410367</v>
+        <v>7.0759247221637428E-2</v>
       </c>
       <c r="G23">
-        <v>0.3077272637854154</v>
-      </c>
-      <c r="H23">
-        <v>0.33997949760891</v>
+        <v>0.2087219756706413</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.30275152934932181</v>
       </c>
       <c r="I23">
-        <v>0.3571745328183167</v>
+        <v>0.3365893813770543</v>
       </c>
       <c r="J23">
-        <v>0.3749224052706704</v>
+        <v>0.34926963155199409</v>
       </c>
       <c r="K23">
-        <v>0.3690144964077461</v>
+        <v>0.37143979460726101</v>
       </c>
       <c r="L23">
-        <v>0.3623151035989186</v>
+        <v>0.36919242317369277</v>
       </c>
       <c r="M23">
-        <v>0.3464388218896167</v>
+        <v>0.36023852597998202</v>
       </c>
       <c r="N23">
-        <v>0.3404914154570609</v>
+        <v>0.34620178983156003</v>
       </c>
       <c r="O23">
-        <v>0.3365238836832427</v>
+        <v>0.34138889844584303</v>
       </c>
       <c r="P23">
-        <v>0.3188225708429546</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.33785996925799883</v>
+      </c>
+      <c r="Q23">
+        <v>0.31562063979240113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>-0.03704864118662871</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C24">
-        <v>-0.002002338917554225</v>
+        <v>-6.7037821502683517E-2</v>
       </c>
       <c r="D24">
-        <v>0.05932466672562654</v>
+        <v>-0.1211297380930431</v>
       </c>
       <c r="E24">
-        <v>-0.01286902784468392</v>
+        <v>-0.17473235489378669</v>
       </c>
       <c r="F24">
-        <v>-0.03004712281138456</v>
+        <v>-0.13884512127843049</v>
       </c>
       <c r="G24">
-        <v>-0.08407976969448272</v>
+        <v>-0.11882376820735351</v>
       </c>
       <c r="H24">
-        <v>-0.07419585036678898</v>
+        <v>-6.5066392197234285E-2</v>
       </c>
       <c r="I24">
-        <v>-0.1008812543978504</v>
+        <v>-0.11443860085593729</v>
       </c>
       <c r="J24">
-        <v>-0.178393088025166</v>
-      </c>
-      <c r="K24">
-        <v>-0.32477519089324</v>
+        <v>-6.0516531396052543E-2</v>
+      </c>
+      <c r="K24" s="2">
+        <v>9.0520078037308577E-2</v>
       </c>
       <c r="L24">
-        <v>-0.3172201425195673</v>
+        <v>0.19273077200024141</v>
       </c>
       <c r="M24">
-        <v>-0.3514604612904818</v>
+        <v>0.22657146651340779</v>
       </c>
       <c r="N24">
-        <v>-0.4465053461935005</v>
+        <v>0.20167201937817369</v>
       </c>
       <c r="O24">
-        <v>-0.5200335447926416</v>
+        <v>0.13898333446254771</v>
       </c>
       <c r="P24">
-        <v>-0.6291734173444823</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>7.6363376262435889E-2</v>
+      </c>
+      <c r="Q24">
+        <v>-5.4217166748831754E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>-0.1538840890504212</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C25">
-        <v>-0.09835657641436842</v>
+        <v>-6.9168112258287159E-2</v>
       </c>
       <c r="D25">
-        <v>-0.108564905364894</v>
+        <v>-0.12723025468056359</v>
       </c>
       <c r="E25">
-        <v>-0.08699783951237504</v>
+        <v>-0.18667424921330031</v>
       </c>
       <c r="F25">
-        <v>-0.1400483703015639</v>
+        <v>-0.14134548534711869</v>
       </c>
       <c r="G25">
-        <v>-0.2098346658443764</v>
+        <v>-0.1130199697290044</v>
       </c>
       <c r="H25">
-        <v>-0.2100571360642922</v>
+        <v>-0.1051298116416808</v>
       </c>
       <c r="I25">
-        <v>-0.1694189313138174</v>
+        <v>-0.20205735691453741</v>
       </c>
       <c r="J25">
-        <v>-0.2110169390920211</v>
+        <v>-0.1322392797236939</v>
       </c>
       <c r="K25">
-        <v>-0.3059412987308207</v>
-      </c>
-      <c r="L25">
-        <v>-0.3597690442681867</v>
+        <v>-5.1218294655323522E-2</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0.15254965903773199</v>
       </c>
       <c r="M25">
-        <v>-0.4557987830411553</v>
+        <v>0.18120652857560579</v>
       </c>
       <c r="N25">
-        <v>-0.5670208490379528</v>
+        <v>0.1967348248035766</v>
       </c>
       <c r="O25">
-        <v>-0.6198940909768103</v>
+        <v>0.16659725145039689</v>
       </c>
       <c r="P25">
-        <v>-0.6587941394194394</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1153935420798107</v>
+      </c>
+      <c r="Q25">
+        <v>4.3003357856149567E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>-0.06769430620935239</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C26">
-        <v>-0.03155757069003653</v>
+        <v>-6.9967703104700477E-2</v>
       </c>
       <c r="D26">
-        <v>0.04522458476251955</v>
+        <v>-0.13866945590639379</v>
       </c>
       <c r="E26">
-        <v>0.06624728714623511</v>
+        <v>-0.14920280475908321</v>
       </c>
       <c r="F26">
-        <v>0.07952192304942816</v>
+        <v>-9.294768280101677E-2</v>
       </c>
       <c r="G26">
-        <v>0.114604609246579</v>
+        <v>-0.13484320116106219</v>
       </c>
       <c r="H26">
-        <v>0.1279840957462619</v>
+        <v>-9.5581128280556149E-2</v>
       </c>
       <c r="I26">
-        <v>0.1319066326383234</v>
+        <v>1.564010526320719E-2</v>
       </c>
       <c r="J26">
-        <v>0.1682671328457477</v>
-      </c>
-      <c r="K26">
-        <v>0.200951297503126</v>
+        <v>-4.7254081067588397E-2</v>
+      </c>
+      <c r="K26" s="2">
+        <v>8.9585595702724202E-2</v>
       </c>
       <c r="L26">
-        <v>0.1704369540537202</v>
+        <v>0.17305619337912659</v>
       </c>
       <c r="M26">
-        <v>0.1894170947358042</v>
+        <v>0.18497572168862009</v>
       </c>
       <c r="N26">
-        <v>0.1624707189988562</v>
+        <v>0.16341194899637659</v>
       </c>
       <c r="O26">
-        <v>0.1391649537943931</v>
+        <v>0.1290106641845031</v>
       </c>
       <c r="P26">
-        <v>0.139093383117885</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>6.5155448331074992E-2</v>
+      </c>
+      <c r="Q26">
+        <v>-2.1898876257478259E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>-0.1177491306962133</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C27">
-        <v>-0.07936111006377725</v>
+        <v>-6.8357226924847039E-2</v>
       </c>
       <c r="D27">
-        <v>0.1127821438566733</v>
+        <v>-0.1218033043094682</v>
       </c>
       <c r="E27">
-        <v>0.123417757396492</v>
+        <v>-0.13260639866768509</v>
       </c>
       <c r="F27">
-        <v>0.1095093909276492</v>
+        <v>-7.4347437975750857E-2</v>
       </c>
       <c r="G27">
-        <v>0.1031714104304308</v>
+        <v>-0.1089463426233238</v>
       </c>
       <c r="H27">
-        <v>0.09469399050862777</v>
+        <v>-7.7168383845713479E-2</v>
       </c>
       <c r="I27">
-        <v>0.05453247405299842</v>
+        <v>1.5300630864306939E-2</v>
       </c>
       <c r="J27">
-        <v>0.1003498755139523</v>
+        <v>-3.4961591454740017E-2</v>
       </c>
       <c r="K27">
-        <v>0.1131704319528546</v>
-      </c>
-      <c r="L27">
-        <v>0.1453961880174357</v>
+        <v>7.018399505714841E-2</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.19732319792215089</v>
       </c>
       <c r="M27">
-        <v>0.1852858585269199</v>
+        <v>0.25971101946596481</v>
       </c>
       <c r="N27">
-        <v>0.1845330164842665</v>
+        <v>0.27815800703373778</v>
       </c>
       <c r="O27">
-        <v>0.1556550667037292</v>
+        <v>0.3000346899826839</v>
       </c>
       <c r="P27">
-        <v>0.1379463004350393</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.27447383799959452</v>
+      </c>
+      <c r="Q27">
+        <v>0.26544946386296842</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>-0.0632991169876408</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C28">
-        <v>-0.1172730905491431</v>
+        <v>-6.7788499615906425E-2</v>
       </c>
       <c r="D28">
-        <v>-0.1726349806042995</v>
+        <v>-0.1203297310582382</v>
       </c>
       <c r="E28">
-        <v>-0.1323277613228749</v>
+        <v>-0.17575414073977019</v>
       </c>
       <c r="F28">
-        <v>-0.1144762218058361</v>
+        <v>-0.13172531177276631</v>
       </c>
       <c r="G28">
-        <v>-0.05941504249098303</v>
+        <v>-0.10985350312049159</v>
       </c>
       <c r="H28">
-        <v>-0.1111156245582144</v>
+        <v>-9.4137034234342304E-2</v>
       </c>
       <c r="I28">
-        <v>-0.05073479102647802</v>
+        <v>-0.1588849826187268</v>
       </c>
       <c r="J28">
-        <v>0.07661386684639453</v>
+        <v>-0.1422836515198703</v>
       </c>
       <c r="K28">
-        <v>0.1949439467972967</v>
-      </c>
-      <c r="L28">
-        <v>0.2283541557249356</v>
+        <v>-7.3565555083535988E-2</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0.15358273934536179</v>
       </c>
       <c r="M28">
-        <v>0.2024768790704256</v>
+        <v>0.19857302750709641</v>
       </c>
       <c r="N28">
-        <v>0.1449732336300044</v>
+        <v>0.23244717161688561</v>
       </c>
       <c r="O28">
-        <v>0.08638835057250711</v>
+        <v>0.24315706019877739</v>
       </c>
       <c r="P28">
-        <v>0.003409890382121704</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.24847264267259631</v>
+      </c>
+      <c r="Q28">
+        <v>0.2471674000982256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>-0.07196788188040393</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C29">
-        <v>-0.1263451147757605</v>
+        <v>-6.925493458772479E-2</v>
       </c>
       <c r="D29">
-        <v>-0.1853313620109307</v>
+        <v>-0.1279818857470762</v>
       </c>
       <c r="E29">
-        <v>-0.1390069977771699</v>
+        <v>-0.18313492071244089</v>
       </c>
       <c r="F29">
-        <v>-0.1158826113618496</v>
+        <v>-0.1362695655210632</v>
       </c>
       <c r="G29">
-        <v>-0.09576157281215601</v>
+        <v>-0.110480903108924</v>
       </c>
       <c r="H29">
-        <v>-0.1871818630358162</v>
+        <v>-8.8331668426214482E-2</v>
       </c>
       <c r="I29">
-        <v>-0.1177998441673872</v>
+        <v>-0.15081693138798791</v>
       </c>
       <c r="J29">
-        <v>-0.0398165057973846</v>
+        <v>-0.1195011097052926</v>
       </c>
       <c r="K29">
-        <v>0.1630119236427803</v>
-      </c>
-      <c r="L29">
-        <v>0.1946879863177396</v>
+        <v>-6.3579036329465669E-2</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0.15382325361070809</v>
       </c>
       <c r="M29">
-        <v>0.2148545580193726</v>
+        <v>0.20355288903853169</v>
       </c>
       <c r="N29">
-        <v>0.1884002797957177</v>
+        <v>0.24111514094010611</v>
       </c>
       <c r="O29">
-        <v>0.1367678550590738</v>
+        <v>0.25437547277563688</v>
       </c>
       <c r="P29">
-        <v>0.07205838668401079</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.26751181157699078</v>
+      </c>
+      <c r="Q29">
+        <v>0.26772437543376959</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>-0.06820513997892179</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C30">
-        <v>-0.1284330252703835</v>
+        <v>-6.9867133635566417E-2</v>
       </c>
       <c r="D30">
-        <v>-0.1413239421058465</v>
+        <v>-0.1258406834585642</v>
       </c>
       <c r="E30">
-        <v>-0.08127428697157135</v>
+        <v>-0.1791152496232761</v>
       </c>
       <c r="F30">
-        <v>-0.1285553506051063</v>
+        <v>-0.13543572287393171</v>
       </c>
       <c r="G30">
-        <v>-0.0917413188328708</v>
+        <v>-0.1174432106078393</v>
       </c>
       <c r="H30">
-        <v>0.008786651344780058</v>
+        <v>-9.8552998377280168E-2</v>
       </c>
       <c r="I30">
-        <v>-0.05189460781608372</v>
+        <v>-0.15860657508985229</v>
       </c>
       <c r="J30">
-        <v>0.08542049197444335</v>
+        <v>-0.13420445951025239</v>
       </c>
       <c r="K30">
-        <v>0.1746613578725854</v>
-      </c>
-      <c r="L30">
-        <v>0.1920376319685738</v>
+        <v>-7.8299448088702095E-2</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0.1336209992746534</v>
       </c>
       <c r="M30">
-        <v>0.1727758125080888</v>
+        <v>0.18789183928544101</v>
       </c>
       <c r="N30">
-        <v>0.1366976301183994</v>
+        <v>0.21984521044118391</v>
       </c>
       <c r="O30">
-        <v>0.07136848068773045</v>
+        <v>0.2472860650449008</v>
       </c>
       <c r="P30">
-        <v>-0.01427525921144934</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.26250541047613968</v>
+      </c>
+      <c r="Q30">
+        <v>0.27310326082877079</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>-0.06870663570746816</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C31">
-        <v>-0.135707065632097</v>
+        <v>-6.9208123815460779E-2</v>
       </c>
       <c r="D31">
-        <v>-0.1502166609367696</v>
+        <v>-0.1202151018858995</v>
       </c>
       <c r="E31">
-        <v>-0.09180169800958521</v>
+        <v>-0.17553946266251719</v>
       </c>
       <c r="F31">
-        <v>-0.1263864416903532</v>
+        <v>-0.13114231167906709</v>
       </c>
       <c r="G31">
-        <v>-0.09989851253912072</v>
+        <v>-0.1107378785386781</v>
       </c>
       <c r="H31">
-        <v>0.001074478903998138</v>
+        <v>-9.1418656550493277E-2</v>
       </c>
       <c r="I31">
-        <v>-0.07005202890519818</v>
+        <v>-0.15959087018148541</v>
       </c>
       <c r="J31">
-        <v>0.05342118177142945</v>
+        <v>-0.13091928091056609</v>
       </c>
       <c r="K31">
-        <v>0.1904718640678881</v>
-      </c>
-      <c r="L31">
-        <v>0.2506366605116659</v>
+        <v>-8.2684691395821394E-2</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0.1078901359590346</v>
       </c>
       <c r="M31">
-        <v>0.28578657963637</v>
+        <v>0.17177194327710721</v>
       </c>
       <c r="N31">
-        <v>0.3004243207230877</v>
+        <v>0.208001370672215</v>
       </c>
       <c r="O31">
-        <v>0.2713710449747964</v>
+        <v>0.23620312643450339</v>
       </c>
       <c r="P31">
-        <v>0.2672551840714802</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.25414912691902919</v>
+      </c>
+      <c r="Q31">
+        <v>0.28030337809209571</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>-0.06859594505090776</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C32">
-        <v>-0.1213314881623954</v>
+        <v>-6.6995635784906346E-2</v>
       </c>
       <c r="D32">
-        <v>-0.1771534559419859</v>
+        <v>-0.1257774030819282</v>
       </c>
       <c r="E32">
-        <v>-0.1318607279293237</v>
+        <v>-0.18129848777895749</v>
       </c>
       <c r="F32">
-        <v>-0.112314809775858</v>
+        <v>-0.14016834298659811</v>
       </c>
       <c r="G32">
-        <v>-0.09721119758310345</v>
+        <v>-0.1129361239181494</v>
       </c>
       <c r="H32">
-        <v>-0.1641335290817526</v>
+        <v>-9.4631465807572757E-2</v>
       </c>
       <c r="I32">
-        <v>-0.1334759373032737</v>
+        <v>-0.16649648273464659</v>
       </c>
       <c r="J32">
-        <v>-0.06980341848804272</v>
+        <v>-0.12837550526124489</v>
       </c>
       <c r="K32">
-        <v>0.1347600666480337</v>
-      </c>
-      <c r="L32">
-        <v>0.1934858914475961</v>
+        <v>-6.8908150038546209E-2</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0.14818952138598071</v>
       </c>
       <c r="M32">
-        <v>0.2227309699209402</v>
+        <v>0.199846088972367</v>
       </c>
       <c r="N32">
-        <v>0.2438827665366646</v>
+        <v>0.226295325971752</v>
       </c>
       <c r="O32">
-        <v>0.242348523228873</v>
+        <v>0.22805723413874951</v>
       </c>
       <c r="P32">
-        <v>0.2439521585617669</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.20951668968739021</v>
+      </c>
+      <c r="Q32">
+        <v>0.18849092799032069</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>-0.07036897738487655</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C33">
-        <v>-0.1263309138545373</v>
+        <v>-6.6346068199675132E-2</v>
       </c>
       <c r="D33">
-        <v>-0.1805692241981733</v>
+        <v>-0.1205868622120467</v>
       </c>
       <c r="E33">
-        <v>-0.1355897630033474</v>
+        <v>-0.1751445221087502</v>
       </c>
       <c r="F33">
-        <v>-0.1140028018707257</v>
+        <v>-0.12853158198751</v>
       </c>
       <c r="G33">
-        <v>-0.08853019301788766</v>
+        <v>-0.10575579306626599</v>
       </c>
       <c r="H33">
-        <v>-0.1524610618094583</v>
+        <v>-8.7415772449075946E-2</v>
       </c>
       <c r="I33">
-        <v>-0.1174742260544559</v>
+        <v>-0.16249240982362839</v>
       </c>
       <c r="J33">
-        <v>-0.05695712387994414</v>
+        <v>-0.12271491902008939</v>
       </c>
       <c r="K33">
-        <v>0.1569104610474031</v>
-      </c>
-      <c r="L33">
-        <v>0.2081470236714941</v>
+        <v>-6.0080294316644037E-2</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0.15360951965428599</v>
       </c>
       <c r="M33">
-        <v>0.2400377928718302</v>
+        <v>0.19618492753100869</v>
       </c>
       <c r="N33">
-        <v>0.2616902778732573</v>
+        <v>0.22914068900599899</v>
       </c>
       <c r="O33">
-        <v>0.2735577487026976</v>
+        <v>0.23597907536953761</v>
       </c>
       <c r="P33">
-        <v>0.2797437532114339</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.2296745673259791</v>
+      </c>
+      <c r="Q33">
+        <v>0.21554769082473249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>-0.06477972953569183</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C34">
-        <v>-0.1202359181252856</v>
+        <v>-6.5478810606256183E-2</v>
       </c>
       <c r="D34">
-        <v>-0.1780635537894118</v>
+        <v>-0.12381593451444819</v>
       </c>
       <c r="E34">
-        <v>-0.136086799783359</v>
+        <v>-0.17923078634830411</v>
       </c>
       <c r="F34">
-        <v>-0.1086013436232022</v>
+        <v>-0.13966845047474219</v>
       </c>
       <c r="G34">
-        <v>-0.08689985619288525</v>
+        <v>-0.11447911175867891</v>
       </c>
       <c r="H34">
-        <v>-0.1542448600861833</v>
+        <v>-9.5975212873211285E-2</v>
       </c>
       <c r="I34">
-        <v>-0.1295109162250171</v>
+        <v>-0.1597843244855669</v>
       </c>
       <c r="J34">
-        <v>-0.07298023806954683</v>
+        <v>-0.13977554382902749</v>
       </c>
       <c r="K34">
-        <v>0.1322908915018159</v>
-      </c>
-      <c r="L34">
-        <v>0.1913387604796723</v>
+        <v>-7.7066974184765991E-2</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0.13451301773905949</v>
       </c>
       <c r="M34">
-        <v>0.2277903447694553</v>
+        <v>0.19025318544556019</v>
       </c>
       <c r="N34">
-        <v>0.2442521896184235</v>
+        <v>0.22033781393516649</v>
       </c>
       <c r="O34">
-        <v>0.2603460709151706</v>
+        <v>0.23261019601306929</v>
       </c>
       <c r="P34">
-        <v>0.2672428206104647</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.22734587441141821</v>
+      </c>
+      <c r="Q34">
+        <v>0.21607017930425901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>-0.06790359372289742</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C35">
-        <v>-0.1273036036303487</v>
+        <v>-7.1347264886246861E-2</v>
       </c>
       <c r="D35">
-        <v>-0.1834179561283044</v>
+        <v>-0.13413224594931039</v>
       </c>
       <c r="E35">
-        <v>-0.1408448801758455</v>
+        <v>-0.18659202980902309</v>
       </c>
       <c r="F35">
-        <v>-0.1201896392944322</v>
+        <v>-0.14299361790365001</v>
       </c>
       <c r="G35">
-        <v>-0.1013665555359216</v>
+        <v>-0.12110571770162119</v>
       </c>
       <c r="H35">
-        <v>-0.1701584875691325</v>
+        <v>-0.10529732385209629</v>
       </c>
       <c r="I35">
-        <v>-0.1526963503378759</v>
+        <v>-0.17246063812549031</v>
       </c>
       <c r="J35">
-        <v>-0.1028148443600772</v>
+        <v>-0.14522860353221009</v>
       </c>
       <c r="K35">
-        <v>0.09212965610655255</v>
-      </c>
-      <c r="L35">
-        <v>0.1599783713314962</v>
+        <v>-8.315190743135252E-2</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0.1269899538524456</v>
       </c>
       <c r="M35">
-        <v>0.1984236331966803</v>
+        <v>0.17194448095013359</v>
       </c>
       <c r="N35">
-        <v>0.2325993538599241</v>
+        <v>0.21030375769927909</v>
       </c>
       <c r="O35">
-        <v>0.2462679976127063</v>
+        <v>0.228873348113006</v>
       </c>
       <c r="P35">
-        <v>0.2724713821490897</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.22895077469241301</v>
+      </c>
+      <c r="Q35">
+        <v>0.22623103359394431</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>-0.07213391851144066</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C36">
-        <v>-0.1351381094511152</v>
+        <v>-6.5952331535988465E-2</v>
       </c>
       <c r="D36">
-        <v>-0.1861796798324898</v>
+        <v>-0.12585013932801989</v>
       </c>
       <c r="E36">
-        <v>-0.1380635306930806</v>
+        <v>-0.178952125008636</v>
       </c>
       <c r="F36">
-        <v>-0.1213255157727176</v>
+        <v>-0.1296427963328724</v>
       </c>
       <c r="G36">
-        <v>-0.1031196871506879</v>
+        <v>-0.1099447372623515</v>
       </c>
       <c r="H36">
-        <v>-0.1816512023480471</v>
+        <v>-9.1635326612509282E-2</v>
       </c>
       <c r="I36">
-        <v>-0.1336578699415704</v>
+        <v>-0.13877267267771901</v>
       </c>
       <c r="J36">
-        <v>-0.06871182882532151</v>
+        <v>-0.1176623650850316</v>
       </c>
       <c r="K36">
-        <v>0.1525699599214748</v>
-      </c>
-      <c r="L36">
-        <v>0.2001574959473314</v>
+        <v>-6.3915791716989592E-2</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0.100162807668013</v>
       </c>
       <c r="M36">
-        <v>0.2393891922822466</v>
+        <v>0.17423404614360141</v>
       </c>
       <c r="N36">
-        <v>0.247664877492109</v>
+        <v>0.20829267995699241</v>
       </c>
       <c r="O36">
-        <v>0.2357844166244329</v>
+        <v>0.2392308209042126</v>
       </c>
       <c r="P36">
-        <v>0.2179801808868348</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.2451761874261115</v>
+      </c>
+      <c r="Q36">
+        <v>0.27197591756875772</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>-0.06454228510022107</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C37">
-        <v>-0.1170581244658114</v>
+        <v>-0.11314841908058609</v>
       </c>
       <c r="D37">
-        <v>-0.1685230307634781</v>
+        <v>-0.18461026284053039</v>
       </c>
       <c r="E37">
-        <v>-0.1286991140679777</v>
+        <v>-0.1132089283984192</v>
       </c>
       <c r="F37">
-        <v>-0.1026973343568726</v>
+        <v>-2.634164952313435E-2</v>
       </c>
       <c r="G37">
-        <v>-0.08700583672619647</v>
+        <v>-8.1310458828502949E-2</v>
       </c>
       <c r="H37">
-        <v>-0.1526654126139095</v>
+        <v>-2.659456159423049E-2</v>
       </c>
       <c r="I37">
-        <v>-0.1210936745463851</v>
+        <v>7.0115015798232219E-2</v>
       </c>
       <c r="J37">
-        <v>-0.06027440656875037</v>
+        <v>0.1027445526995107</v>
       </c>
       <c r="K37">
-        <v>0.1549736812785978</v>
+        <v>9.3239678595555306E-2</v>
       </c>
       <c r="L37">
-        <v>0.2009921909146425</v>
+        <v>9.7469245515093048E-2</v>
       </c>
       <c r="M37">
-        <v>0.2350732631338462</v>
+        <v>8.3002397072095876E-2</v>
       </c>
       <c r="N37">
-        <v>0.2383605441085976</v>
+        <v>4.0433215464465593E-2</v>
       </c>
       <c r="O37">
-        <v>0.2339551979577679</v>
+        <v>6.8211537433813987E-2</v>
       </c>
       <c r="P37">
-        <v>0.215000919759591</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>7.1900083490852945E-2</v>
+      </c>
+      <c r="Q37">
+        <v>7.4831741125298681E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>-0.06840291074110766</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C38">
-        <v>-0.1240253908900541</v>
+        <v>-8.9226837138832837E-2</v>
       </c>
       <c r="D38">
-        <v>-0.1757527072770099</v>
+        <v>-0.1713105567637255</v>
       </c>
       <c r="E38">
-        <v>-0.1260678251495131</v>
+        <v>-0.14544493790042509</v>
       </c>
       <c r="F38">
-        <v>-0.1042532588916724</v>
+        <v>-1.144965434834171E-2</v>
       </c>
       <c r="G38">
-        <v>-0.08192876986831378</v>
+        <v>1.0498748906429141E-2</v>
       </c>
       <c r="H38">
-        <v>-0.1414770221243416</v>
-      </c>
-      <c r="I38">
-        <v>-0.1153480303952318</v>
+        <v>0.1442370850776527</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0.2775675146089806</v>
       </c>
       <c r="J38">
-        <v>-0.05413327439363137</v>
+        <v>0.26757450541673611</v>
       </c>
       <c r="K38">
-        <v>0.1506842528625256</v>
+        <v>0.22444575173848491</v>
       </c>
       <c r="L38">
-        <v>0.1989662170504564</v>
+        <v>0.18226281402768921</v>
       </c>
       <c r="M38">
-        <v>0.2298094633009626</v>
+        <v>0.18220114204189711</v>
       </c>
       <c r="N38">
-        <v>0.2416132513100487</v>
+        <v>0.16386215651528191</v>
       </c>
       <c r="O38">
-        <v>0.250967047710334</v>
+        <v>0.16523474019553991</v>
       </c>
       <c r="P38">
-        <v>0.2307279913714461</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.18303504876808621</v>
+      </c>
+      <c r="Q38">
+        <v>0.196992134001686</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>-0.07056549107845415</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C39">
-        <v>-0.1285210767342237</v>
+        <v>-8.3528659657616425E-2</v>
       </c>
       <c r="D39">
-        <v>-0.1809159051540844</v>
+        <v>-0.1500533259893084</v>
       </c>
       <c r="E39">
-        <v>-0.1384791670646799</v>
+        <v>-0.117167995271697</v>
       </c>
       <c r="F39">
-        <v>-0.1113555858077296</v>
+        <v>7.1627543799385783E-3</v>
       </c>
       <c r="G39">
-        <v>-0.09427409692311653</v>
-      </c>
-      <c r="H39">
-        <v>-0.1604388020159296</v>
+        <v>2.0566796750604459E-2</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0.1238650501950322</v>
       </c>
       <c r="I39">
-        <v>-0.1280778490391062</v>
+        <v>0.24515856695666949</v>
       </c>
       <c r="J39">
-        <v>-0.06580792466900268</v>
+        <v>0.23715032466795261</v>
       </c>
       <c r="K39">
-        <v>0.1405305281617102</v>
+        <v>0.25029905760195448</v>
       </c>
       <c r="L39">
-        <v>0.1864114933886935</v>
+        <v>0.2356809172994391</v>
       </c>
       <c r="M39">
-        <v>0.2232575210656438</v>
+        <v>0.22068664496770099</v>
       </c>
       <c r="N39">
-        <v>0.2334214865097475</v>
+        <v>0.23839279331835991</v>
       </c>
       <c r="O39">
-        <v>0.238274921913971</v>
+        <v>0.22498494970686131</v>
       </c>
       <c r="P39">
-        <v>0.2251361479085535</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.21362124862329609</v>
+      </c>
+      <c r="Q39">
+        <v>0.21482441780216691</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>-0.07008391229590191</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C40">
-        <v>-0.1246390809867833</v>
+        <v>-0.11661024487017389</v>
       </c>
       <c r="D40">
-        <v>-0.1746652881136437</v>
+        <v>-8.1966766744247882E-2</v>
       </c>
       <c r="E40">
-        <v>-0.1315818480630474</v>
+        <v>-3.9481700469426919E-3</v>
       </c>
       <c r="F40">
-        <v>-0.1114689274671427</v>
-      </c>
-      <c r="G40">
-        <v>-0.09157122030274076</v>
+        <v>-3.2925514391594933E-2</v>
+      </c>
+      <c r="G40" s="2">
+        <v>9.1072753435794296E-2</v>
       </c>
       <c r="H40">
-        <v>-0.1539180825266186</v>
+        <v>0.15588100703969129</v>
       </c>
       <c r="I40">
-        <v>-0.1265828903320223</v>
+        <v>0.15489885112216401</v>
       </c>
       <c r="J40">
-        <v>-0.07101044696595016</v>
+        <v>0.1130362057577257</v>
       </c>
       <c r="K40">
-        <v>0.1193249762433043</v>
+        <v>0.10726051572115999</v>
       </c>
       <c r="L40">
-        <v>0.1806939235331631</v>
+        <v>0.14335305667957041</v>
       </c>
       <c r="M40">
-        <v>0.2126597009920072</v>
+        <v>0.13789721647859929</v>
       </c>
       <c r="N40">
-        <v>0.2443278447232455</v>
+        <v>0.15886491830936661</v>
       </c>
       <c r="O40">
-        <v>0.2574297301517016</v>
+        <v>0.14132269101058009</v>
       </c>
       <c r="P40">
-        <v>0.285306998278389</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1100970986740491</v>
+      </c>
+      <c r="Q40">
+        <v>4.8130582253516963E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>-0.1127519278908456</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C41">
-        <v>-0.1845773529806243</v>
+        <v>-0.1235405999514196</v>
       </c>
       <c r="D41">
-        <v>-0.1184118162536127</v>
+        <v>-0.28052814749204003</v>
       </c>
       <c r="E41">
-        <v>-0.03027874800478101</v>
+        <v>-0.18997653962224459</v>
       </c>
       <c r="F41">
-        <v>-0.09083468429934198</v>
+        <v>-0.18660092583652599</v>
       </c>
       <c r="G41">
-        <v>-0.03910743668687505</v>
+        <v>-0.11112017287628589</v>
       </c>
       <c r="H41">
-        <v>0.05673137510353959</v>
+        <v>-9.0492564931809724E-2</v>
       </c>
       <c r="I41">
-        <v>0.09344685230918105</v>
+        <v>-6.7135748907148782E-2</v>
       </c>
       <c r="J41">
-        <v>0.08805539735379699</v>
+        <v>-1.8675278563536419E-2</v>
       </c>
       <c r="K41">
-        <v>0.09597523839040595</v>
+        <v>-4.800443550544374E-2</v>
       </c>
       <c r="L41">
-        <v>0.07856245089623937</v>
+        <v>-8.4198630505543048E-2</v>
       </c>
       <c r="M41">
-        <v>0.03635912311581341</v>
+        <v>-7.3439615843409481E-2</v>
       </c>
       <c r="N41">
-        <v>0.05804176653357994</v>
+        <v>-9.6631210210212731E-2</v>
       </c>
       <c r="O41">
-        <v>0.06104655999312882</v>
+        <v>-0.15650709797987769</v>
       </c>
       <c r="P41">
-        <v>0.06051774178649963</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>-0.16569907969029851</v>
+      </c>
+      <c r="Q41">
+        <v>-0.182050892754022</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>-0.08440044907419667</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C42">
-        <v>-0.1675190824107607</v>
+        <v>-2.2890052509304759E-2</v>
       </c>
       <c r="D42">
-        <v>-0.1398854879172394</v>
+        <v>-0.3114616594391908</v>
       </c>
       <c r="E42">
-        <v>0.00692453690087527</v>
+        <v>-0.17910916306563049</v>
       </c>
       <c r="F42">
-        <v>0.02751265382431337</v>
+        <v>5.1333041460466057E-2</v>
       </c>
       <c r="G42">
-        <v>0.1520614114160024</v>
-      </c>
-      <c r="H42">
-        <v>0.2694625255723068</v>
+        <v>0.12615840611262699</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0.16633414527963919</v>
       </c>
       <c r="I42">
-        <v>0.2674576804399398</v>
+        <v>0.25145587147385923</v>
       </c>
       <c r="J42">
-        <v>0.2262830983381858</v>
+        <v>0.26455859170394991</v>
       </c>
       <c r="K42">
-        <v>0.182329053233986</v>
+        <v>0.24257189264877169</v>
       </c>
       <c r="L42">
-        <v>0.1772643719741785</v>
+        <v>0.26909331928317182</v>
       </c>
       <c r="M42">
-        <v>0.1641928142385302</v>
+        <v>0.26795261822349831</v>
       </c>
       <c r="N42">
-        <v>0.1722982993747066</v>
+        <v>0.24592209556783459</v>
       </c>
       <c r="O42">
-        <v>0.191339176233025</v>
+        <v>0.23677739076381149</v>
       </c>
       <c r="P42">
-        <v>0.20324972746184</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.2376222746998316</v>
+      </c>
+      <c r="Q42">
+        <v>0.22433337204694531</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>-0.08597604976404595</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C43">
-        <v>-0.1546324534342996</v>
+        <v>-6.7061822434962656E-2</v>
       </c>
       <c r="D43">
-        <v>-0.1149410956345632</v>
+        <v>-0.11312176862108041</v>
       </c>
       <c r="E43">
-        <v>-0.0008803011178764366</v>
+        <v>-2.7095629536232731E-2</v>
       </c>
       <c r="F43">
-        <v>0.00996190530208178</v>
-      </c>
-      <c r="G43">
-        <v>0.1131506245529324</v>
+        <v>1.7182183855057782E-2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.1720585570423491</v>
       </c>
       <c r="H43">
-        <v>0.2462991809072786</v>
+        <v>0.22219006026362381</v>
       </c>
       <c r="I43">
-        <v>0.2382626887641737</v>
+        <v>0.25294254787862208</v>
       </c>
       <c r="J43">
-        <v>0.2452430414473566</v>
+        <v>0.23574792308444331</v>
       </c>
       <c r="K43">
-        <v>0.2361838302333045</v>
+        <v>0.19776829396609291</v>
       </c>
       <c r="L43">
-        <v>0.2284034506572804</v>
+        <v>0.2421722150478916</v>
       </c>
       <c r="M43">
-        <v>0.2445248373235854</v>
+        <v>0.24922934268282179</v>
       </c>
       <c r="N43">
-        <v>0.2331139510721605</v>
+        <v>0.25579267808371953</v>
       </c>
       <c r="O43">
-        <v>0.2150877334648108</v>
+        <v>0.23380387942614139</v>
       </c>
       <c r="P43">
-        <v>0.2208504471999504</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>-0.1166150191957296</v>
-      </c>
-      <c r="C44">
-        <v>-0.08568569649923771</v>
-      </c>
-      <c r="D44">
-        <v>0.004241334884028187</v>
-      </c>
-      <c r="E44">
-        <v>-0.02672946074656941</v>
-      </c>
-      <c r="F44">
-        <v>0.09349631760754616</v>
-      </c>
-      <c r="G44">
-        <v>0.1589402298102576</v>
-      </c>
-      <c r="H44">
-        <v>0.1531402466899255</v>
-      </c>
-      <c r="I44">
-        <v>0.1142779581220505</v>
-      </c>
-      <c r="J44">
-        <v>0.1091444274164673</v>
-      </c>
-      <c r="K44">
-        <v>0.1454036879137126</v>
-      </c>
-      <c r="L44">
-        <v>0.1345505032154251</v>
-      </c>
-      <c r="M44">
-        <v>0.1491375208018433</v>
-      </c>
-      <c r="N44">
-        <v>0.1305526886593856</v>
-      </c>
-      <c r="O44">
-        <v>0.1014556306136801</v>
-      </c>
-      <c r="P44">
-        <v>0.04702939450096773</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>-0.1168745423532851</v>
-      </c>
-      <c r="C45">
-        <v>-0.2878704572774627</v>
-      </c>
-      <c r="D45">
-        <v>-0.187799904839801</v>
-      </c>
-      <c r="E45">
-        <v>-0.1827139760012107</v>
-      </c>
-      <c r="F45">
-        <v>-0.1094907254695904</v>
-      </c>
-      <c r="G45">
-        <v>-0.08701596080538532</v>
-      </c>
-      <c r="H45">
-        <v>-0.06740292888462764</v>
-      </c>
-      <c r="I45">
-        <v>-0.0220511961196147</v>
-      </c>
-      <c r="J45">
-        <v>-0.04786607318354291</v>
-      </c>
-      <c r="K45">
-        <v>-0.08034205116146197</v>
-      </c>
-      <c r="L45">
-        <v>-0.07656221969087972</v>
-      </c>
-      <c r="M45">
-        <v>-0.09775330883981496</v>
-      </c>
-      <c r="N45">
-        <v>-0.1516917517577817</v>
-      </c>
-      <c r="O45">
-        <v>-0.1604993568501385</v>
-      </c>
-      <c r="P45">
-        <v>-0.180704494734979</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>-0.01943771833120427</v>
-      </c>
-      <c r="C46">
-        <v>-0.299451301671645</v>
-      </c>
-      <c r="D46">
-        <v>-0.1637327707003554</v>
-      </c>
-      <c r="E46">
-        <v>0.06748415787772552</v>
-      </c>
-      <c r="F46">
-        <v>0.1315146608101442</v>
-      </c>
-      <c r="G46">
-        <v>0.1766658110622349</v>
-      </c>
-      <c r="H46">
-        <v>0.261042633687149</v>
-      </c>
-      <c r="I46">
-        <v>0.2687420795085405</v>
-      </c>
-      <c r="J46">
-        <v>0.2531381398036313</v>
-      </c>
-      <c r="K46">
-        <v>0.2746311490115388</v>
-      </c>
-      <c r="L46">
-        <v>0.2689749068005968</v>
-      </c>
-      <c r="M46">
-        <v>0.2480267432609486</v>
-      </c>
-      <c r="N46">
-        <v>0.243573162467696</v>
-      </c>
-      <c r="O46">
-        <v>0.2436665003420025</v>
-      </c>
-      <c r="P46">
-        <v>0.2261691810490173</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>-0.07951112901220371</v>
-      </c>
-      <c r="C47">
-        <v>-0.1261401422125008</v>
-      </c>
-      <c r="D47">
-        <v>-0.02653928998160474</v>
-      </c>
-      <c r="E47">
-        <v>0.005104004100517</v>
-      </c>
-      <c r="F47">
-        <v>0.1722873209920882</v>
-      </c>
-      <c r="G47">
-        <v>0.21971059705037</v>
-      </c>
-      <c r="H47">
-        <v>0.2591090234908717</v>
-      </c>
-      <c r="I47">
-        <v>0.2463352691423425</v>
-      </c>
-      <c r="J47">
-        <v>0.2146271440582259</v>
-      </c>
-      <c r="K47">
-        <v>0.248397337859013</v>
-      </c>
-      <c r="L47">
-        <v>0.2491990064580432</v>
-      </c>
-      <c r="M47">
-        <v>0.2495246518748516</v>
-      </c>
-      <c r="N47">
-        <v>0.2274615478490895</v>
-      </c>
-      <c r="O47">
-        <v>0.2108466063230614</v>
-      </c>
-      <c r="P47">
-        <v>0.1858888790251586</v>
+        <v>0.2125542043203715</v>
+      </c>
+      <c r="Q43">
+        <v>0.19609457945016981</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:Q43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>